--- a/2 четверть_3_Программист_Java.xlsx
+++ b/2 четверть_3_Программист_Java.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Machenike\Desktop\GB_Developer_Workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADDC9A0-C0E2-43FF-9D54-AB3FB261E5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE2486D-8EFF-44EF-BB00-352B9810EAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Java 1-6" sheetId="12" r:id="rId1"/>
@@ -22,6 +22,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -25156,12 +25159,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="77" x14ac:knownFonts="1">
+  <fonts count="78" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -26195,7 +26206,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -26217,32 +26228,32 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26266,16 +26277,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26287,13 +26298,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26308,10 +26319,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26326,19 +26337,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26347,13 +26358,13 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26365,43 +26376,43 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26410,31 +26421,31 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="37" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -26442,7 +26453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -26466,13 +26477,13 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26484,7 +26495,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -26493,13 +26504,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="61" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="62" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26508,13 +26519,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26530,7 +26541,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26548,7 +26559,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26563,16 +26574,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26584,16 +26595,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -26611,13 +26622,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26626,7 +26637,7 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26647,22 +26658,22 @@
     <xf numFmtId="49" fontId="0" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="45" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26677,22 +26688,22 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26730,82 +26741,82 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26820,55 +26831,55 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -26883,7 +26894,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -26895,128 +26906,134 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="74" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -27025,14 +27042,11 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -27043,52 +27057,49 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -28292,15 +28303,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>92364</xdr:colOff>
+      <xdr:colOff>125293</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>207819</xdr:rowOff>
+      <xdr:rowOff>44533</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>3775364</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>119975</xdr:rowOff>
+      <xdr:colOff>3800673</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>2162951</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -28323,8 +28334,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="63061273" y="57681092"/>
-          <a:ext cx="3683000" cy="2132842"/>
+          <a:off x="61874507" y="66801176"/>
+          <a:ext cx="3675380" cy="2118418"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -28989,44 +29000,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC545"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="73.81640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="43.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.90625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="66.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.81640625" style="11" customWidth="1"/>
-    <col min="11" max="11" width="39.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="92.453125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="60.54296875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.81640625" style="11" customWidth="1"/>
-    <col min="16" max="16" width="56.81640625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="54.36328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="58.81640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.81640625" style="12"/>
-    <col min="21" max="21" width="67.81640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.36328125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.36328125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6328125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.1796875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="125.08984375" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="48.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="73.77734375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="66.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="11" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="92.44140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="60.5546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="11" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="54.33203125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="58.77734375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="12"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="125.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
@@ -29045,7 +29056,7 @@
       <c r="S2" s="8"/>
       <c r="U2" s="8"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -29053,7 +29064,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -29073,7 +29084,7 @@
       </c>
       <c r="V4" s="2"/>
     </row>
-    <row r="5" spans="1:23" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="76" t="s">
         <v>321</v>
       </c>
@@ -29110,7 +29121,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="87" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>18</v>
       </c>
@@ -29138,7 +29149,7 @@
       </c>
       <c r="N6" s="20"/>
     </row>
-    <row r="7" spans="1:23" ht="116" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>23</v>
       </c>
@@ -29172,7 +29183,7 @@
       <c r="U7" s="1"/>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="1:23" ht="116" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="95" t="s">
         <v>25</v>
       </c>
@@ -29207,7 +29218,7 @@
       <c r="S8" s="2"/>
       <c r="V8" s="2"/>
     </row>
-    <row r="9" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>2205</v>
       </c>
@@ -29227,7 +29238,7 @@
       <c r="S9" s="2"/>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="1:23" ht="140.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" ht="140.55000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="104" t="s">
         <v>69</v>
       </c>
@@ -29262,7 +29273,7 @@
       <c r="R10" s="14"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:23" ht="222.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" ht="222.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="99" t="s">
         <v>48</v>
       </c>
@@ -29295,7 +29306,7 @@
       </c>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:23" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:23" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="36"/>
       <c r="B12" s="22"/>
       <c r="C12" s="24" t="s">
@@ -29337,7 +29348,7 @@
       </c>
       <c r="S12" s="43"/>
     </row>
-    <row r="13" spans="1:23" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>52</v>
       </c>
@@ -29380,7 +29391,7 @@
       <c r="S13" s="35"/>
       <c r="V13" s="2"/>
     </row>
-    <row r="14" spans="1:23" ht="131" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:23" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="36"/>
       <c r="B14" s="22"/>
       <c r="C14" s="61" t="s">
@@ -29420,7 +29431,7 @@
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" spans="1:23" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:23" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89" t="s">
         <v>746</v>
       </c>
@@ -29461,7 +29472,7 @@
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
     </row>
-    <row r="16" spans="1:23" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="103" t="s">
         <v>397</v>
       </c>
@@ -29509,7 +29520,7 @@
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
         <v>862</v>
       </c>
@@ -29553,7 +29564,7 @@
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
         <v>863</v>
       </c>
@@ -29597,7 +29608,7 @@
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
     </row>
-    <row r="19" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
         <v>864</v>
       </c>
@@ -29642,7 +29653,7 @@
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
         <v>865</v>
       </c>
@@ -29685,7 +29696,7 @@
       <c r="S20" s="35"/>
       <c r="U20" s="1"/>
     </row>
-    <row r="21" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:23" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="34" t="s">
         <v>866</v>
       </c>
@@ -29728,7 +29739,7 @@
       <c r="S21" s="35"/>
       <c r="U21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="87" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
         <v>867</v>
       </c>
@@ -29773,7 +29784,7 @@
       <c r="S22" s="35"/>
       <c r="U22" s="1"/>
     </row>
-    <row r="23" spans="1:23" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:23" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="34" t="s">
         <v>868</v>
       </c>
@@ -29820,7 +29831,7 @@
       <c r="S23" s="35"/>
       <c r="U23" s="1"/>
     </row>
-    <row r="24" spans="1:23" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:23" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="34" t="s">
         <v>869</v>
       </c>
@@ -29865,7 +29876,7 @@
       <c r="S24" s="35"/>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" spans="1:23" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="34" t="s">
         <v>870</v>
       </c>
@@ -29910,7 +29921,7 @@
       <c r="S25" s="35"/>
       <c r="U25" s="1"/>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="34" t="s">
         <v>871</v>
       </c>
@@ -29953,7 +29964,7 @@
       <c r="S26" s="35"/>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" spans="1:23" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:23" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="34" t="s">
         <v>872</v>
       </c>
@@ -30000,7 +30011,7 @@
       <c r="S27" s="35"/>
       <c r="U27" s="1"/>
     </row>
-    <row r="28" spans="1:23" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="34" t="s">
         <v>873</v>
       </c>
@@ -30045,7 +30056,7 @@
       <c r="S28" s="35"/>
       <c r="U28" s="1"/>
     </row>
-    <row r="29" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:23" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="34" t="s">
         <v>874</v>
       </c>
@@ -30091,7 +30102,7 @@
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
     </row>
-    <row r="30" spans="1:23" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="34" t="s">
         <v>875</v>
       </c>
@@ -30137,7 +30148,7 @@
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
     </row>
-    <row r="31" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34" t="s">
         <v>876</v>
       </c>
@@ -30181,7 +30192,7 @@
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
     </row>
-    <row r="32" spans="1:23" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:23" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="34" t="s">
         <v>877</v>
       </c>
@@ -30227,7 +30238,7 @@
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>878</v>
       </c>
@@ -30271,7 +30282,7 @@
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
     </row>
-    <row r="34" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="34" t="s">
         <v>879</v>
       </c>
@@ -30315,7 +30326,7 @@
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" s="34" t="s">
         <v>880</v>
       </c>
@@ -30361,7 +30372,7 @@
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
     </row>
-    <row r="36" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="34" t="s">
         <v>881</v>
       </c>
@@ -30405,7 +30416,7 @@
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
     </row>
-    <row r="37" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34" t="s">
         <v>882</v>
       </c>
@@ -30444,7 +30455,7 @@
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
     </row>
-    <row r="38" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="34" t="s">
         <v>883</v>
       </c>
@@ -30488,7 +30499,7 @@
       <c r="V38" s="2"/>
       <c r="W38" s="2"/>
     </row>
-    <row r="39" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="34" t="s">
         <v>884</v>
       </c>
@@ -30532,7 +30543,7 @@
       <c r="V39" s="2"/>
       <c r="W39" s="2"/>
     </row>
-    <row r="40" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="34" t="s">
         <v>885</v>
       </c>
@@ -30576,7 +30587,7 @@
       <c r="V40" s="2"/>
       <c r="W40" s="2"/>
     </row>
-    <row r="41" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="34" t="s">
         <v>886</v>
       </c>
@@ -30620,7 +30631,7 @@
       <c r="V41" s="2"/>
       <c r="W41" s="2"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" s="34" t="s">
         <v>887</v>
       </c>
@@ -30666,7 +30677,7 @@
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" s="34" t="s">
         <v>889</v>
       </c>
@@ -30710,7 +30721,7 @@
       <c r="V43" s="2"/>
       <c r="W43" s="2"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" s="34" t="s">
         <v>890</v>
       </c>
@@ -30754,7 +30765,7 @@
       <c r="V44" s="2"/>
       <c r="W44" s="2"/>
     </row>
-    <row r="45" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="34" t="s">
         <v>892</v>
       </c>
@@ -30798,7 +30809,7 @@
       <c r="V45" s="2"/>
       <c r="W45" s="2"/>
     </row>
-    <row r="46" spans="1:23" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:23" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="34" t="s">
         <v>894</v>
       </c>
@@ -30844,7 +30855,7 @@
       <c r="V46" s="2"/>
       <c r="W46" s="2"/>
     </row>
-    <row r="47" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="34" t="s">
         <v>895</v>
       </c>
@@ -30888,7 +30899,7 @@
       <c r="V47" s="2"/>
       <c r="W47" s="2"/>
     </row>
-    <row r="48" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="34" t="s">
         <v>896</v>
       </c>
@@ -30934,7 +30945,7 @@
       <c r="V48" s="2"/>
       <c r="W48" s="2"/>
     </row>
-    <row r="49" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="34" t="s">
         <v>897</v>
       </c>
@@ -30978,7 +30989,7 @@
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
     </row>
-    <row r="50" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="34" t="s">
         <v>898</v>
       </c>
@@ -31022,7 +31033,7 @@
       <c r="V50" s="2"/>
       <c r="W50" s="2"/>
     </row>
-    <row r="51" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="34" t="s">
         <v>899</v>
       </c>
@@ -31066,7 +31077,7 @@
       <c r="V51" s="2"/>
       <c r="W51" s="2"/>
     </row>
-    <row r="52" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="34" t="s">
         <v>900</v>
       </c>
@@ -31110,7 +31121,7 @@
       <c r="V52" s="2"/>
       <c r="W52" s="2"/>
     </row>
-    <row r="53" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="34" t="s">
         <v>901</v>
       </c>
@@ -31153,7 +31164,7 @@
       <c r="S53" s="35"/>
       <c r="U53" s="1"/>
     </row>
-    <row r="54" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="34" t="s">
         <v>902</v>
       </c>
@@ -31198,7 +31209,7 @@
       <c r="S54" s="35"/>
       <c r="U54" s="1"/>
     </row>
-    <row r="55" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="34" t="s">
         <v>903</v>
       </c>
@@ -31241,7 +31252,7 @@
       <c r="S55" s="35"/>
       <c r="U55" s="1"/>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" s="34" t="s">
         <v>904</v>
       </c>
@@ -31284,7 +31295,7 @@
       <c r="S56" s="35"/>
       <c r="U56" s="1"/>
     </row>
-    <row r="57" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="34" t="s">
         <v>905</v>
       </c>
@@ -31327,7 +31338,7 @@
       <c r="S57" s="35"/>
       <c r="U57" s="1"/>
     </row>
-    <row r="58" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="34" t="s">
         <v>906</v>
       </c>
@@ -31370,7 +31381,7 @@
       <c r="S58" s="35"/>
       <c r="U58" s="1"/>
     </row>
-    <row r="59" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="34" t="s">
         <v>907</v>
       </c>
@@ -31415,7 +31426,7 @@
       <c r="S59" s="35"/>
       <c r="U59" s="1"/>
     </row>
-    <row r="60" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="34" t="s">
         <v>908</v>
       </c>
@@ -31458,7 +31469,7 @@
       <c r="S60" s="35"/>
       <c r="U60" s="1"/>
     </row>
-    <row r="61" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="34" t="s">
         <v>909</v>
       </c>
@@ -31501,7 +31512,7 @@
       <c r="S61" s="35"/>
       <c r="U61" s="1"/>
     </row>
-    <row r="62" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="34" t="s">
         <v>910</v>
       </c>
@@ -31544,7 +31555,7 @@
       <c r="S62" s="35"/>
       <c r="U62" s="1"/>
     </row>
-    <row r="63" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="34" t="s">
         <v>911</v>
       </c>
@@ -31587,7 +31598,7 @@
       <c r="S63" s="35"/>
       <c r="U63" s="1"/>
     </row>
-    <row r="64" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="34" t="s">
         <v>912</v>
       </c>
@@ -31634,7 +31645,7 @@
       <c r="V64"/>
       <c r="W64"/>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" s="34" t="s">
         <v>913</v>
       </c>
@@ -31681,7 +31692,7 @@
       <c r="V65"/>
       <c r="W65"/>
     </row>
-    <row r="66" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:23" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="34" t="s">
         <v>914</v>
       </c>
@@ -31728,7 +31739,7 @@
       <c r="V66"/>
       <c r="W66"/>
     </row>
-    <row r="67" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A67" s="34" t="s">
         <v>916</v>
       </c>
@@ -31766,7 +31777,7 @@
       <c r="V67"/>
       <c r="W67"/>
     </row>
-    <row r="68" spans="1:23" ht="58" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A68" s="34" t="s">
         <v>918</v>
       </c>
@@ -31806,7 +31817,7 @@
       <c r="V68"/>
       <c r="W68"/>
     </row>
-    <row r="69" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="34" t="s">
         <v>919</v>
       </c>
@@ -31844,7 +31855,7 @@
       <c r="V69"/>
       <c r="W69"/>
     </row>
-    <row r="70" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="34" t="s">
         <v>920</v>
       </c>
@@ -31884,7 +31895,7 @@
       <c r="V70"/>
       <c r="W70"/>
     </row>
-    <row r="71" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="34" t="s">
         <v>921</v>
       </c>
@@ -31922,7 +31933,7 @@
       <c r="V71"/>
       <c r="W71"/>
     </row>
-    <row r="72" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="34" t="s">
         <v>922</v>
       </c>
@@ -31958,7 +31969,7 @@
       <c r="S72" s="35"/>
       <c r="V72" s="2"/>
     </row>
-    <row r="73" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="34" t="s">
         <v>923</v>
       </c>
@@ -31995,7 +32006,7 @@
       <c r="V73" s="2"/>
       <c r="W73" s="2"/>
     </row>
-    <row r="74" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="64" t="s">
         <v>924</v>
       </c>
@@ -32032,7 +32043,7 @@
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
     </row>
-    <row r="75" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="64" t="s">
         <v>925</v>
       </c>
@@ -32069,7 +32080,7 @@
       <c r="V75" s="2"/>
       <c r="W75" s="2"/>
     </row>
-    <row r="76" spans="1:23" ht="58" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="64" t="s">
         <v>926</v>
       </c>
@@ -32108,7 +32119,7 @@
       <c r="V76" s="2"/>
       <c r="W76" s="2"/>
     </row>
-    <row r="77" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" s="64" t="s">
         <v>377</v>
       </c>
@@ -32145,7 +32156,7 @@
       <c r="V77" s="2"/>
       <c r="W77" s="2"/>
     </row>
-    <row r="78" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="64" t="s">
         <v>927</v>
       </c>
@@ -32182,7 +32193,7 @@
       <c r="V78" s="2"/>
       <c r="W78" s="2"/>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" s="64" t="s">
         <v>928</v>
       </c>
@@ -32219,7 +32230,7 @@
       <c r="V79" s="2"/>
       <c r="W79" s="2"/>
     </row>
-    <row r="80" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="64" t="s">
         <v>929</v>
       </c>
@@ -32253,7 +32264,7 @@
       <c r="V80" s="2"/>
       <c r="W80" s="2"/>
     </row>
-    <row r="81" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="64" t="s">
         <v>930</v>
       </c>
@@ -32287,7 +32298,7 @@
       <c r="V81" s="2"/>
       <c r="W81" s="2"/>
     </row>
-    <row r="82" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" s="64" t="s">
         <v>931</v>
       </c>
@@ -32321,7 +32332,7 @@
       <c r="V82" s="2"/>
       <c r="W82" s="2"/>
     </row>
-    <row r="83" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" s="64" t="s">
         <v>932</v>
       </c>
@@ -32356,7 +32367,7 @@
       <c r="V83" s="2"/>
       <c r="W83" s="2"/>
     </row>
-    <row r="84" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="64" t="s">
         <v>933</v>
       </c>
@@ -32392,7 +32403,7 @@
       <c r="V84" s="2"/>
       <c r="W84" s="2"/>
     </row>
-    <row r="85" spans="1:23" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:23" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="64" t="s">
         <v>934</v>
       </c>
@@ -32428,7 +32439,7 @@
       <c r="V85" s="2"/>
       <c r="W85" s="2"/>
     </row>
-    <row r="86" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" s="64" t="s">
         <v>935</v>
       </c>
@@ -32458,7 +32469,7 @@
       <c r="V86" s="2"/>
       <c r="W86" s="2"/>
     </row>
-    <row r="87" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="64" t="s">
         <v>936</v>
       </c>
@@ -32486,7 +32497,7 @@
       <c r="V87" s="2"/>
       <c r="W87" s="2"/>
     </row>
-    <row r="88" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="64" t="s">
         <v>937</v>
       </c>
@@ -32514,7 +32525,7 @@
       <c r="V88" s="2"/>
       <c r="W88" s="2"/>
     </row>
-    <row r="89" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="64" t="s">
         <v>938</v>
       </c>
@@ -32540,7 +32551,7 @@
       </c>
       <c r="S89" s="35"/>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90" s="34" t="s">
         <v>939</v>
       </c>
@@ -32566,7 +32577,7 @@
       </c>
       <c r="S90" s="35"/>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91" s="34" t="s">
         <v>940</v>
       </c>
@@ -32592,7 +32603,7 @@
       </c>
       <c r="S91" s="35"/>
     </row>
-    <row r="92" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="34" t="s">
         <v>941</v>
       </c>
@@ -32618,7 +32629,7 @@
       </c>
       <c r="S92" s="35"/>
     </row>
-    <row r="93" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" s="34" t="s">
         <v>942</v>
       </c>
@@ -32644,7 +32655,7 @@
       </c>
       <c r="S93" s="35"/>
     </row>
-    <row r="94" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="34" t="s">
         <v>943</v>
       </c>
@@ -32670,7 +32681,7 @@
       </c>
       <c r="S94" s="35"/>
     </row>
-    <row r="95" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="34" t="s">
         <v>944</v>
       </c>
@@ -32696,7 +32707,7 @@
       </c>
       <c r="S95" s="35"/>
     </row>
-    <row r="96" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="36" t="s">
         <v>945</v>
       </c>
@@ -32722,7 +32733,7 @@
       </c>
       <c r="S96" s="37"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
       <c r="F97"/>
@@ -32733,7 +32744,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
       <c r="F98"/>
@@ -32748,7 +32759,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
       <c r="F99"/>
@@ -32763,7 +32774,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
       <c r="F100"/>
@@ -32778,7 +32789,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
       <c r="F101"/>
@@ -32793,7 +32804,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
       <c r="F102"/>
@@ -32808,7 +32819,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
       <c r="F103"/>
@@ -32820,7 +32831,7 @@
       <c r="M103"/>
       <c r="N103" s="2"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
       <c r="H104" s="79"/>
@@ -32830,7 +32841,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="8"/>
       <c r="C105" s="9"/>
@@ -32849,7 +32860,7 @@
       <c r="S105" s="8"/>
       <c r="U105" s="8"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>125</v>
       </c>
@@ -32857,7 +32868,7 @@
       <c r="U106" s="1"/>
       <c r="V106" s="2"/>
     </row>
-    <row r="107" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>0</v>
       </c>
@@ -32877,7 +32888,7 @@
       </c>
       <c r="V107" s="2"/>
     </row>
-    <row r="108" spans="1:24" ht="276" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:24" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="88" t="s">
         <v>118</v>
       </c>
@@ -32935,7 +32946,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="109" spans="1:24" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:24" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="121" t="s">
         <v>121</v>
       </c>
@@ -32995,7 +33006,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:24" ht="203" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:24" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A110" s="164" t="s">
         <v>2187</v>
       </c>
@@ -33036,7 +33047,7 @@
       <c r="S110" s="35"/>
       <c r="U110" s="1"/>
     </row>
-    <row r="111" spans="1:24" ht="319.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:24" ht="317.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="115" t="s">
         <v>2188</v>
       </c>
@@ -33080,7 +33091,7 @@
       <c r="S111" s="37"/>
       <c r="U111" s="1"/>
     </row>
-    <row r="112" spans="1:24" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:24" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="116" t="s">
         <v>60</v>
       </c>
@@ -33119,7 +33130,7 @@
       </c>
       <c r="U112" s="1"/>
     </row>
-    <row r="113" spans="1:29" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:29" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F113" s="244" t="s">
         <v>2214</v>
       </c>
@@ -33139,7 +33150,7 @@
       <c r="S113" s="35"/>
       <c r="U113" s="1"/>
     </row>
-    <row r="114" spans="1:29" ht="261.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:29" ht="259.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="F114" s="2" t="s">
@@ -33169,7 +33180,7 @@
       </c>
       <c r="U114" s="1"/>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="F115" s="4" t="s">
@@ -33182,7 +33193,7 @@
       <c r="S115" s="2"/>
       <c r="U115" s="1"/>
     </row>
-    <row r="116" spans="1:29" ht="116" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:29" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="G116" s="1" t="s">
@@ -33197,7 +33208,7 @@
       <c r="R116" s="1"/>
       <c r="U116" s="1"/>
     </row>
-    <row r="117" spans="1:29" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:29" ht="72" x14ac:dyDescent="0.3">
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="G117" s="1" t="s">
@@ -33212,7 +33223,7 @@
       <c r="R117" s="1"/>
       <c r="U117" s="1"/>
     </row>
-    <row r="118" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:29" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="G118" s="1" t="s">
@@ -33227,7 +33238,7 @@
       <c r="R118" s="1"/>
       <c r="U118" s="1"/>
     </row>
-    <row r="119" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:29" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="G119" s="1" t="s">
@@ -33242,7 +33253,7 @@
       <c r="R119" s="1"/>
       <c r="U119" s="1"/>
     </row>
-    <row r="120" spans="1:29" ht="156.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:29" ht="156.44999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="131" t="s">
         <v>738</v>
       </c>
@@ -33301,7 +33312,7 @@
       <c r="AB120" s="25"/>
       <c r="AC120" s="25"/>
     </row>
-    <row r="121" spans="1:29" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:29" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="88" t="s">
         <v>712</v>
       </c>
@@ -33364,7 +33375,7 @@
       <c r="AB121" s="25"/>
       <c r="AC121" s="25"/>
     </row>
-    <row r="122" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:29" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="89" t="s">
         <v>689</v>
       </c>
@@ -33411,7 +33422,7 @@
       <c r="AB122" s="25"/>
       <c r="AC122" s="25"/>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A123" s="34" t="s">
         <v>690</v>
       </c>
@@ -33462,7 +33473,7 @@
       <c r="AB123" s="25"/>
       <c r="AC123" s="25"/>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A124" s="34" t="s">
         <v>692</v>
       </c>
@@ -33513,7 +33524,7 @@
       <c r="AB124" s="25"/>
       <c r="AC124" s="25"/>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A125" s="34" t="s">
         <v>694</v>
       </c>
@@ -33564,7 +33575,7 @@
       <c r="AB125" s="25"/>
       <c r="AC125" s="25"/>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A126" s="34" t="s">
         <v>697</v>
       </c>
@@ -33615,7 +33626,7 @@
       <c r="AB126" s="25"/>
       <c r="AC126" s="25"/>
     </row>
-    <row r="127" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="34" t="s">
         <v>699</v>
       </c>
@@ -33666,7 +33677,7 @@
       <c r="AB127" s="25"/>
       <c r="AC127" s="25"/>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A128" s="34" t="s">
         <v>701</v>
       </c>
@@ -33708,7 +33719,7 @@
       <c r="AB128" s="25"/>
       <c r="AC128" s="25"/>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A129" s="34" t="s">
         <v>703</v>
       </c>
@@ -33750,7 +33761,7 @@
       <c r="AB129" s="25"/>
       <c r="AC129" s="25"/>
     </row>
-    <row r="130" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="34" t="s">
         <v>705</v>
       </c>
@@ -33792,7 +33803,7 @@
       <c r="AB130" s="25"/>
       <c r="AC130" s="25"/>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A131" s="34" t="s">
         <v>707</v>
       </c>
@@ -33828,7 +33839,7 @@
       <c r="AB131" s="25"/>
       <c r="AC131" s="25"/>
     </row>
-    <row r="132" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="36" t="s">
         <v>709</v>
       </c>
@@ -33864,7 +33875,7 @@
       <c r="AB132" s="25"/>
       <c r="AC132" s="25"/>
     </row>
-    <row r="133" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G133" s="1"/>
       <c r="K133" s="36" t="s">
         <v>1415</v>
@@ -33889,21 +33900,21 @@
       <c r="AB133" s="25"/>
       <c r="AC133" s="25"/>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
       <c r="G134" s="1"/>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="U134" s="1"/>
     </row>
-    <row r="135" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G135" s="1"/>
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="U135" s="1"/>
     </row>
-    <row r="136" spans="1:29" ht="87" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:29" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A136" s="89" t="s">
         <v>680</v>
       </c>
@@ -33934,7 +33945,7 @@
       <c r="S136" s="43"/>
       <c r="U136" s="1"/>
     </row>
-    <row r="137" spans="1:29" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:29" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="34" t="s">
         <v>154</v>
       </c>
@@ -33975,7 +33986,7 @@
       <c r="S137" s="35"/>
       <c r="U137" s="1"/>
     </row>
-    <row r="138" spans="1:29" ht="58" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A138" s="89" t="s">
         <v>2056</v>
       </c>
@@ -34020,7 +34031,7 @@
       <c r="S138" s="35"/>
       <c r="U138" s="1"/>
     </row>
-    <row r="139" spans="1:29" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:29" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="36" t="s">
         <v>2080</v>
       </c>
@@ -34063,7 +34074,7 @@
       <c r="S139" s="35"/>
       <c r="U139" s="1"/>
     </row>
-    <row r="140" spans="1:29" ht="58" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A140" s="34" t="s">
         <v>682</v>
       </c>
@@ -34108,7 +34119,7 @@
       <c r="S140" s="35"/>
       <c r="U140" s="1"/>
     </row>
-    <row r="141" spans="1:29" ht="58" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:29" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A141" s="34" t="s">
         <v>683</v>
       </c>
@@ -34153,7 +34164,7 @@
       <c r="S141" s="35"/>
       <c r="U141" s="1"/>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A142" s="34" t="s">
         <v>1100</v>
       </c>
@@ -34196,7 +34207,7 @@
       <c r="S142" s="35"/>
       <c r="U142" s="1"/>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A143" s="34" t="s">
         <v>1101</v>
       </c>
@@ -34239,7 +34250,7 @@
       <c r="S143" s="35"/>
       <c r="U143" s="1"/>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A144" s="34" t="s">
         <v>1102</v>
       </c>
@@ -34282,7 +34293,7 @@
       <c r="S144" s="35"/>
       <c r="U144" s="1"/>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A145" s="34" t="s">
         <v>1103</v>
       </c>
@@ -34325,7 +34336,7 @@
       <c r="S145" s="35"/>
       <c r="U145" s="1"/>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A146" s="34" t="s">
         <v>1104</v>
       </c>
@@ -34368,7 +34379,7 @@
       <c r="S146" s="35"/>
       <c r="U146" s="1"/>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147" s="34" t="s">
         <v>1105</v>
       </c>
@@ -34411,7 +34422,7 @@
       <c r="S147" s="35"/>
       <c r="U147" s="1"/>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A148" s="34" t="s">
         <v>1106</v>
       </c>
@@ -34454,7 +34465,7 @@
       <c r="S148" s="35"/>
       <c r="U148" s="1"/>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A149" s="34" t="s">
         <v>1107</v>
       </c>
@@ -34497,7 +34508,7 @@
       <c r="S149" s="35"/>
       <c r="U149" s="1"/>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A150" s="34" t="s">
         <v>1108</v>
       </c>
@@ -34540,7 +34551,7 @@
       <c r="S150" s="35"/>
       <c r="U150" s="1"/>
     </row>
-    <row r="151" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="34" t="s">
         <v>1109</v>
       </c>
@@ -34583,7 +34594,7 @@
       <c r="S151" s="37"/>
       <c r="U151" s="1"/>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="34" t="s">
         <v>1110</v>
       </c>
@@ -34619,7 +34630,7 @@
       <c r="R152" s="1"/>
       <c r="U152" s="1"/>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A153" s="34" t="s">
         <v>1111</v>
       </c>
@@ -34655,7 +34666,7 @@
       <c r="R153" s="1"/>
       <c r="U153" s="1"/>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A154" s="34" t="s">
         <v>1112</v>
       </c>
@@ -34691,7 +34702,7 @@
       <c r="R154" s="1"/>
       <c r="U154" s="1"/>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A155" s="34" t="s">
         <v>1113</v>
       </c>
@@ -34727,7 +34738,7 @@
       <c r="R155" s="1"/>
       <c r="U155" s="1"/>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A156" s="34" t="s">
         <v>1114</v>
       </c>
@@ -34763,7 +34774,7 @@
       <c r="R156" s="1"/>
       <c r="U156" s="1"/>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="34" t="s">
         <v>1115</v>
       </c>
@@ -34799,7 +34810,7 @@
       <c r="R157" s="1"/>
       <c r="U157" s="1"/>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A158" s="34" t="s">
         <v>1116</v>
       </c>
@@ -34835,7 +34846,7 @@
       <c r="R158" s="1"/>
       <c r="U158" s="1"/>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A159" s="34" t="s">
         <v>1117</v>
       </c>
@@ -34871,7 +34882,7 @@
       <c r="R159" s="1"/>
       <c r="U159" s="1"/>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A160" s="129" t="s">
         <v>1118</v>
       </c>
@@ -34907,7 +34918,7 @@
       <c r="R160" s="1"/>
       <c r="U160" s="1"/>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="52" t="s">
         <v>1120</v>
       </c>
@@ -34943,7 +34954,7 @@
       <c r="R161" s="1"/>
       <c r="U161" s="1"/>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="52" t="s">
         <v>1122</v>
       </c>
@@ -34979,7 +34990,7 @@
       <c r="R162" s="1"/>
       <c r="U162" s="1"/>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" s="52" t="s">
         <v>1124</v>
       </c>
@@ -35015,7 +35026,7 @@
       <c r="R163" s="1"/>
       <c r="U163" s="1"/>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" s="52" t="s">
         <v>1126</v>
       </c>
@@ -35051,7 +35062,7 @@
       <c r="R164" s="1"/>
       <c r="U164" s="1"/>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" s="52" t="s">
         <v>1128</v>
       </c>
@@ -35087,7 +35098,7 @@
       <c r="R165" s="1"/>
       <c r="U165" s="1"/>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" s="52" t="s">
         <v>1130</v>
       </c>
@@ -35123,7 +35134,7 @@
       <c r="R166" s="1"/>
       <c r="U166" s="1"/>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" s="52" t="s">
         <v>1132</v>
       </c>
@@ -35159,7 +35170,7 @@
       <c r="R167" s="1"/>
       <c r="U167" s="1"/>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" s="52" t="s">
         <v>1134</v>
       </c>
@@ -35195,7 +35206,7 @@
       <c r="R168" s="1"/>
       <c r="U168" s="1"/>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" s="52" t="s">
         <v>1136</v>
       </c>
@@ -35231,7 +35242,7 @@
       <c r="R169" s="1"/>
       <c r="U169" s="1"/>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" s="52" t="s">
         <v>1138</v>
       </c>
@@ -35267,7 +35278,7 @@
       <c r="R170" s="1"/>
       <c r="U170" s="1"/>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" s="52" t="s">
         <v>1140</v>
       </c>
@@ -35303,7 +35314,7 @@
       <c r="R171" s="1"/>
       <c r="U171" s="1"/>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" s="52" t="s">
         <v>1142</v>
       </c>
@@ -35339,7 +35350,7 @@
       <c r="R172" s="1"/>
       <c r="U172" s="1"/>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" s="52" t="s">
         <v>1144</v>
       </c>
@@ -35375,7 +35386,7 @@
       <c r="R173" s="1"/>
       <c r="U173" s="1"/>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" s="52" t="s">
         <v>1146</v>
       </c>
@@ -35411,7 +35422,7 @@
       <c r="R174" s="1"/>
       <c r="U174" s="1"/>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" s="52" t="s">
         <v>1148</v>
       </c>
@@ -35447,7 +35458,7 @@
       <c r="R175" s="1"/>
       <c r="U175" s="1"/>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A176" s="52" t="s">
         <v>1150</v>
       </c>
@@ -35483,7 +35494,7 @@
       <c r="R176" s="1"/>
       <c r="U176" s="1"/>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A177" s="52" t="s">
         <v>1152</v>
       </c>
@@ -35519,7 +35530,7 @@
       <c r="R177" s="1"/>
       <c r="U177" s="1"/>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A178" s="52" t="s">
         <v>1153</v>
       </c>
@@ -35555,7 +35566,7 @@
       <c r="R178" s="1"/>
       <c r="U178" s="1"/>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A179" s="130" t="s">
         <v>1155</v>
       </c>
@@ -35591,7 +35602,7 @@
       <c r="R179" s="1"/>
       <c r="U179" s="1"/>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A180" s="34" t="s">
         <v>1157</v>
       </c>
@@ -35627,7 +35638,7 @@
       <c r="R180" s="1"/>
       <c r="U180" s="1"/>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A181" s="34" t="s">
         <v>1159</v>
       </c>
@@ -35663,7 +35674,7 @@
       <c r="R181" s="1"/>
       <c r="U181" s="1"/>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A182" s="34" t="s">
         <v>1161</v>
       </c>
@@ -35699,7 +35710,7 @@
       <c r="R182" s="1"/>
       <c r="U182" s="1"/>
     </row>
-    <row r="183" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="34" t="s">
         <v>1163</v>
       </c>
@@ -35735,7 +35746,7 @@
       <c r="R183" s="1"/>
       <c r="U183" s="1"/>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A184" s="34" t="s">
         <v>1165</v>
       </c>
@@ -35763,7 +35774,7 @@
       <c r="R184" s="1"/>
       <c r="U184" s="1"/>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A185" s="34" t="s">
         <v>1167</v>
       </c>
@@ -35791,7 +35802,7 @@
       <c r="R185" s="1"/>
       <c r="U185" s="1"/>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A186" s="34" t="s">
         <v>1169</v>
       </c>
@@ -35819,7 +35830,7 @@
       <c r="R186" s="1"/>
       <c r="U186" s="1"/>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A187" s="34" t="s">
         <v>1171</v>
       </c>
@@ -35847,7 +35858,7 @@
       <c r="R187" s="1"/>
       <c r="U187" s="1"/>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A188" s="161" t="s">
         <v>1173</v>
       </c>
@@ -35875,7 +35886,7 @@
       <c r="R188" s="1"/>
       <c r="U188" s="1"/>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A189" s="162" t="s">
         <v>1174</v>
       </c>
@@ -35903,7 +35914,7 @@
       <c r="R189" s="1"/>
       <c r="U189" s="1"/>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A190" s="162" t="s">
         <v>1175</v>
       </c>
@@ -35931,7 +35942,7 @@
       <c r="R190" s="1"/>
       <c r="U190" s="1"/>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A191" s="162" t="s">
         <v>1176</v>
       </c>
@@ -35959,7 +35970,7 @@
       <c r="R191" s="1"/>
       <c r="U191" s="1"/>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A192" s="162" t="s">
         <v>1177</v>
       </c>
@@ -35987,7 +35998,7 @@
       <c r="R192" s="1"/>
       <c r="U192" s="1"/>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A193" s="162" t="s">
         <v>1178</v>
       </c>
@@ -36017,7 +36028,7 @@
       <c r="R193" s="1"/>
       <c r="U193" s="1"/>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A194" s="162" t="s">
         <v>1179</v>
       </c>
@@ -36047,7 +36058,7 @@
       <c r="R194" s="1"/>
       <c r="U194" s="1"/>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A195" s="162" t="s">
         <v>1180</v>
       </c>
@@ -36077,7 +36088,7 @@
       <c r="R195" s="1"/>
       <c r="U195" s="1"/>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A196" s="162" t="s">
         <v>1181</v>
       </c>
@@ -36107,7 +36118,7 @@
       <c r="R196" s="1"/>
       <c r="U196" s="1"/>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A197" s="163" t="s">
         <v>1182</v>
       </c>
@@ -36137,7 +36148,7 @@
       <c r="R197" s="1"/>
       <c r="U197" s="1"/>
     </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A198" s="161" t="s">
         <v>1183</v>
       </c>
@@ -36167,7 +36178,7 @@
       <c r="R198" s="1"/>
       <c r="U198" s="1"/>
     </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A199" s="162" t="s">
         <v>1184</v>
       </c>
@@ -36197,7 +36208,7 @@
       <c r="R199" s="1"/>
       <c r="U199" s="1"/>
     </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A200" s="162" t="s">
         <v>1185</v>
       </c>
@@ -36227,7 +36238,7 @@
       <c r="R200" s="1"/>
       <c r="U200" s="1"/>
     </row>
-    <row r="201" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="162" t="s">
         <v>1186</v>
       </c>
@@ -36257,7 +36268,7 @@
       <c r="R201" s="1"/>
       <c r="U201" s="1"/>
     </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A202" s="162" t="s">
         <v>1187</v>
       </c>
@@ -36277,7 +36288,7 @@
       <c r="R202" s="1"/>
       <c r="U202" s="1"/>
     </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A203" s="162" t="s">
         <v>1188</v>
       </c>
@@ -36297,7 +36308,7 @@
       <c r="R203" s="1"/>
       <c r="U203" s="1"/>
     </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A204" s="162" t="s">
         <v>1189</v>
       </c>
@@ -36317,7 +36328,7 @@
       <c r="R204" s="1"/>
       <c r="U204" s="1"/>
     </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A205" s="162" t="s">
         <v>1190</v>
       </c>
@@ -36337,7 +36348,7 @@
       <c r="R205" s="1"/>
       <c r="U205" s="1"/>
     </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A206" s="162" t="s">
         <v>1191</v>
       </c>
@@ -36357,7 +36368,7 @@
       <c r="R206" s="1"/>
       <c r="U206" s="1"/>
     </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A207" s="163" t="s">
         <v>1192</v>
       </c>
@@ -36377,7 +36388,7 @@
       <c r="R207" s="1"/>
       <c r="U207" s="1"/>
     </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A208" s="34" t="s">
         <v>1193</v>
       </c>
@@ -36397,7 +36408,7 @@
       <c r="R208" s="1"/>
       <c r="U208" s="1"/>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A209" s="34" t="s">
         <v>1194</v>
       </c>
@@ -36417,7 +36428,7 @@
       <c r="R209" s="1"/>
       <c r="U209" s="1"/>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A210" s="34" t="s">
         <v>1195</v>
       </c>
@@ -36437,7 +36448,7 @@
       <c r="R210" s="1"/>
       <c r="U210" s="1"/>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A211" s="129" t="s">
         <v>1196</v>
       </c>
@@ -36457,7 +36468,7 @@
       <c r="R211" s="1"/>
       <c r="U211" s="1"/>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A212" s="52" t="s">
         <v>1197</v>
       </c>
@@ -36477,7 +36488,7 @@
       <c r="R212" s="1"/>
       <c r="U212" s="1"/>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A213" s="52" t="s">
         <v>1199</v>
       </c>
@@ -36497,7 +36508,7 @@
       <c r="R213" s="1"/>
       <c r="U213" s="1"/>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A214" s="52" t="s">
         <v>1200</v>
       </c>
@@ -36517,7 +36528,7 @@
       <c r="R214" s="1"/>
       <c r="U214" s="1"/>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A215" s="52" t="s">
         <v>1202</v>
       </c>
@@ -36537,7 +36548,7 @@
       <c r="R215" s="1"/>
       <c r="U215" s="1"/>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A216" s="52" t="s">
         <v>1203</v>
       </c>
@@ -36557,7 +36568,7 @@
       <c r="R216" s="1"/>
       <c r="U216" s="1"/>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A217" s="52" t="s">
         <v>1205</v>
       </c>
@@ -36577,7 +36588,7 @@
       <c r="R217" s="1"/>
       <c r="U217" s="1"/>
     </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A218" s="52" t="s">
         <v>1206</v>
       </c>
@@ -36597,7 +36608,7 @@
       <c r="R218" s="1"/>
       <c r="U218" s="1"/>
     </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A219" s="52" t="s">
         <v>1208</v>
       </c>
@@ -36617,7 +36628,7 @@
       <c r="R219" s="1"/>
       <c r="U219" s="1"/>
     </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A220" s="52" t="s">
         <v>1209</v>
       </c>
@@ -36637,7 +36648,7 @@
       <c r="R220" s="1"/>
       <c r="U220" s="1"/>
     </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A221" s="52" t="s">
         <v>1211</v>
       </c>
@@ -36657,7 +36668,7 @@
       <c r="R221" s="1"/>
       <c r="U221" s="1"/>
     </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A222" s="52" t="s">
         <v>1212</v>
       </c>
@@ -36677,7 +36688,7 @@
       <c r="R222" s="1"/>
       <c r="U222" s="1"/>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A223" s="52" t="s">
         <v>1214</v>
       </c>
@@ -36697,7 +36708,7 @@
       <c r="R223" s="1"/>
       <c r="U223" s="1"/>
     </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A224" s="52" t="s">
         <v>1216</v>
       </c>
@@ -36717,7 +36728,7 @@
       <c r="R224" s="1"/>
       <c r="U224" s="1"/>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A225" s="52" t="s">
         <v>1217</v>
       </c>
@@ -36737,7 +36748,7 @@
       <c r="R225" s="1"/>
       <c r="U225" s="1"/>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A226" s="52" t="s">
         <v>1219</v>
       </c>
@@ -36757,7 +36768,7 @@
       <c r="R226" s="1"/>
       <c r="U226" s="1"/>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A227" s="52" t="s">
         <v>1220</v>
       </c>
@@ -36777,7 +36788,7 @@
       <c r="R227" s="1"/>
       <c r="U227" s="1"/>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A228" s="52" t="s">
         <v>1222</v>
       </c>
@@ -36797,7 +36808,7 @@
       <c r="R228" s="1"/>
       <c r="U228" s="1"/>
     </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A229" s="52" t="s">
         <v>1224</v>
       </c>
@@ -36817,7 +36828,7 @@
       <c r="R229" s="1"/>
       <c r="U229" s="1"/>
     </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A230" s="130" t="s">
         <v>1225</v>
       </c>
@@ -36837,7 +36848,7 @@
       <c r="R230" s="1"/>
       <c r="U230" s="1"/>
     </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A231" s="52" t="s">
         <v>1226</v>
       </c>
@@ -36857,7 +36868,7 @@
       <c r="R231" s="1"/>
       <c r="U231" s="1"/>
     </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A232" s="52" t="s">
         <v>1227</v>
       </c>
@@ -36877,7 +36888,7 @@
       <c r="R232" s="1"/>
       <c r="U232" s="1"/>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A233" s="52" t="s">
         <v>1228</v>
       </c>
@@ -36897,7 +36908,7 @@
       <c r="R233" s="1"/>
       <c r="U233" s="1"/>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A234" s="52" t="s">
         <v>1229</v>
       </c>
@@ -36917,7 +36928,7 @@
       <c r="R234" s="1"/>
       <c r="U234" s="1"/>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A235" s="52" t="s">
         <v>1230</v>
       </c>
@@ -36937,7 +36948,7 @@
       <c r="R235" s="1"/>
       <c r="U235" s="1"/>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A236" s="52" t="s">
         <v>1231</v>
       </c>
@@ -36957,7 +36968,7 @@
       <c r="R236" s="1"/>
       <c r="U236" s="1"/>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A237" s="52" t="s">
         <v>1232</v>
       </c>
@@ -36977,7 +36988,7 @@
       <c r="R237" s="1"/>
       <c r="U237" s="1"/>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A238" s="52" t="s">
         <v>1233</v>
       </c>
@@ -36997,7 +37008,7 @@
       <c r="R238" s="1"/>
       <c r="U238" s="1"/>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A239" s="52" t="s">
         <v>1234</v>
       </c>
@@ -37017,7 +37028,7 @@
       <c r="R239" s="1"/>
       <c r="U239" s="1"/>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A240" s="52" t="s">
         <v>1235</v>
       </c>
@@ -37037,7 +37048,7 @@
       <c r="R240" s="1"/>
       <c r="U240" s="1"/>
     </row>
-    <row r="241" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A241" s="52" t="s">
         <v>1236</v>
       </c>
@@ -37057,7 +37068,7 @@
       <c r="R241" s="1"/>
       <c r="U241" s="1"/>
     </row>
-    <row r="242" spans="1:22" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:22" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="148" t="s">
         <v>1237</v>
       </c>
@@ -37077,7 +37088,7 @@
       <c r="R242" s="1"/>
       <c r="U242" s="1"/>
     </row>
-    <row r="243" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
       <c r="F243" s="25"/>
@@ -37089,7 +37100,7 @@
       <c r="R243" s="1"/>
       <c r="U243" s="1"/>
     </row>
-    <row r="244" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
       <c r="F244" s="25"/>
@@ -37101,7 +37112,7 @@
       <c r="R244" s="1"/>
       <c r="U244" s="1"/>
     </row>
-    <row r="245" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
       <c r="F245" s="25"/>
@@ -37113,7 +37124,7 @@
       <c r="R245" s="1"/>
       <c r="U245" s="1"/>
     </row>
-    <row r="246" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
       <c r="F246" s="25"/>
@@ -37125,7 +37136,7 @@
       <c r="R246" s="1"/>
       <c r="U246" s="1"/>
     </row>
-    <row r="247" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
       <c r="F247" s="25"/>
@@ -37137,7 +37148,7 @@
       <c r="R247" s="1"/>
       <c r="U247" s="1"/>
     </row>
-    <row r="248" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
       <c r="F248" s="25"/>
@@ -37149,7 +37160,7 @@
       <c r="R248" s="1"/>
       <c r="U248" s="1"/>
     </row>
-    <row r="249" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
       <c r="F249" s="25"/>
@@ -37161,7 +37172,7 @@
       <c r="R249" s="1"/>
       <c r="U249" s="1"/>
     </row>
-    <row r="250" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
       <c r="F250" s="25"/>
@@ -37173,7 +37184,7 @@
       <c r="R250" s="1"/>
       <c r="U250" s="1"/>
     </row>
-    <row r="251" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="F251" s="25"/>
@@ -37185,7 +37196,7 @@
       <c r="R251" s="1"/>
       <c r="U251" s="1"/>
     </row>
-    <row r="252" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
       <c r="F252" s="25"/>
@@ -37197,7 +37208,7 @@
       <c r="R252" s="1"/>
       <c r="U252" s="1"/>
     </row>
-    <row r="253" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
       <c r="B253" s="8"/>
       <c r="C253" s="9"/>
@@ -37216,7 +37227,7 @@
       <c r="S253" s="8"/>
       <c r="U253" s="8"/>
     </row>
-    <row r="254" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>2064</v>
       </c>
@@ -37224,7 +37235,7 @@
       <c r="U254" s="1"/>
       <c r="V254" s="2"/>
     </row>
-    <row r="255" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>0</v>
       </c>
@@ -37247,7 +37258,7 @@
       </c>
       <c r="V255" s="2"/>
     </row>
-    <row r="256" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>1988</v>
       </c>
@@ -37266,7 +37277,7 @@
       <c r="R256" s="1"/>
       <c r="U256" s="1"/>
     </row>
-    <row r="257" spans="1:25" ht="203" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:25" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>1991</v>
       </c>
@@ -37288,7 +37299,7 @@
       <c r="R257" s="1"/>
       <c r="U257" s="1"/>
     </row>
-    <row r="258" spans="1:25" ht="261" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:25" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>1996</v>
       </c>
@@ -37310,7 +37321,7 @@
       <c r="R258" s="1"/>
       <c r="U258" s="1"/>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B259" s="10"/>
       <c r="C259" s="10"/>
       <c r="F259" s="25"/>
@@ -37322,7 +37333,7 @@
       <c r="R259" s="1"/>
       <c r="U259" s="1"/>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B260" s="10"/>
       <c r="C260" s="10"/>
       <c r="F260" s="25"/>
@@ -37334,7 +37345,7 @@
       <c r="R260" s="1"/>
       <c r="U260" s="1"/>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B261" s="10"/>
       <c r="C261" s="10"/>
       <c r="F261" s="25"/>
@@ -37346,7 +37357,7 @@
       <c r="R261" s="1"/>
       <c r="U261" s="1"/>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B262" s="10"/>
       <c r="C262" s="10"/>
       <c r="F262" s="25"/>
@@ -37358,7 +37369,7 @@
       <c r="R262" s="1"/>
       <c r="U262" s="1"/>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B263" s="10"/>
       <c r="C263" s="10"/>
       <c r="F263" s="25"/>
@@ -37370,7 +37381,7 @@
       <c r="R263" s="1"/>
       <c r="U263" s="1"/>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B264" s="10"/>
       <c r="C264" s="10"/>
       <c r="F264" s="25"/>
@@ -37382,7 +37393,7 @@
       <c r="R264" s="1"/>
       <c r="U264" s="1"/>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B265" s="10"/>
       <c r="C265" s="10"/>
       <c r="F265" s="25"/>
@@ -37394,7 +37405,7 @@
       <c r="R265" s="1"/>
       <c r="U265" s="1"/>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
       <c r="F266" s="25"/>
@@ -37406,7 +37417,7 @@
       <c r="R266" s="1"/>
       <c r="U266" s="1"/>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C267" s="10"/>
       <c r="D267" s="10"/>
       <c r="F267" s="10"/>
@@ -37427,7 +37438,7 @@
       <c r="X267" s="10"/>
       <c r="Y267" s="10"/>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A268" s="6"/>
       <c r="B268" s="8"/>
       <c r="C268" s="9"/>
@@ -37446,7 +37457,7 @@
       <c r="S268" s="8"/>
       <c r="U268" s="8"/>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>114</v>
       </c>
@@ -37454,7 +37465,7 @@
       <c r="U269" s="1"/>
       <c r="V269" s="2"/>
     </row>
-    <row r="270" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F270" s="4" t="s">
         <v>1</v>
       </c>
@@ -37468,7 +37479,7 @@
       </c>
       <c r="V270" s="2"/>
     </row>
-    <row r="271" spans="1:25" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:25" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="111" t="s">
         <v>1508</v>
       </c>
@@ -37518,7 +37529,7 @@
       </c>
       <c r="Y271" s="10"/>
     </row>
-    <row r="272" spans="1:25" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:25" ht="244.8" x14ac:dyDescent="0.3">
       <c r="B272" s="62"/>
       <c r="C272" s="2"/>
       <c r="D272" s="62"/>
@@ -37559,7 +37570,7 @@
       <c r="U272" s="1"/>
       <c r="Y272" s="10"/>
     </row>
-    <row r="273" spans="1:25" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:25" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
       <c r="F273" s="34"/>
@@ -37591,7 +37602,7 @@
       <c r="U273" s="1"/>
       <c r="Y273" s="10"/>
     </row>
-    <row r="274" spans="1:25" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:25" ht="187.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="89" t="s">
         <v>1420</v>
       </c>
@@ -37640,7 +37651,7 @@
       <c r="X274" s="10"/>
       <c r="Y274" s="10"/>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A275" s="161" t="s">
         <v>1422</v>
       </c>
@@ -37681,7 +37692,7 @@
       <c r="X275" s="10"/>
       <c r="Y275" s="10"/>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A276" s="162" t="s">
         <v>1424</v>
       </c>
@@ -37722,7 +37733,7 @@
       <c r="X276" s="10"/>
       <c r="Y276" s="10"/>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A277" s="162" t="s">
         <v>1426</v>
       </c>
@@ -37763,7 +37774,7 @@
       <c r="X277" s="10"/>
       <c r="Y277" s="10"/>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A278" s="162" t="s">
         <v>1428</v>
       </c>
@@ -37804,7 +37815,7 @@
       <c r="X278" s="10"/>
       <c r="Y278" s="10"/>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A279" s="162" t="s">
         <v>1430</v>
       </c>
@@ -37845,7 +37856,7 @@
       <c r="X279" s="10"/>
       <c r="Y279" s="10"/>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A280" s="162" t="s">
         <v>1432</v>
       </c>
@@ -37886,7 +37897,7 @@
       <c r="X280" s="10"/>
       <c r="Y280" s="10"/>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A281" s="162" t="s">
         <v>1434</v>
       </c>
@@ -37927,7 +37938,7 @@
       <c r="X281" s="10"/>
       <c r="Y281" s="10"/>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A282" s="162" t="s">
         <v>1436</v>
       </c>
@@ -37968,7 +37979,7 @@
       <c r="X282" s="10"/>
       <c r="Y282" s="10"/>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A283" s="162" t="s">
         <v>1438</v>
       </c>
@@ -38009,7 +38020,7 @@
       <c r="X283" s="10"/>
       <c r="Y283" s="10"/>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A284" s="162" t="s">
         <v>1440</v>
       </c>
@@ -38052,7 +38063,7 @@
       <c r="X284" s="10"/>
       <c r="Y284" s="10"/>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A285" s="162" t="s">
         <v>1442</v>
       </c>
@@ -38093,7 +38104,7 @@
       <c r="X285" s="10"/>
       <c r="Y285" s="10"/>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A286" s="162" t="s">
         <v>1444</v>
       </c>
@@ -38134,7 +38145,7 @@
       <c r="X286" s="10"/>
       <c r="Y286" s="10"/>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A287" s="162" t="s">
         <v>1446</v>
       </c>
@@ -38175,7 +38186,7 @@
       <c r="X287" s="10"/>
       <c r="Y287" s="10"/>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A288" s="163" t="s">
         <v>1448</v>
       </c>
@@ -38216,7 +38227,7 @@
       <c r="X288" s="10"/>
       <c r="Y288" s="10"/>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A289" s="34" t="s">
         <v>1450</v>
       </c>
@@ -38257,7 +38268,7 @@
       <c r="X289" s="10"/>
       <c r="Y289" s="10"/>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A290" s="34" t="s">
         <v>791</v>
       </c>
@@ -38298,7 +38309,7 @@
       <c r="X290" s="10"/>
       <c r="Y290" s="10"/>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A291" s="34" t="s">
         <v>793</v>
       </c>
@@ -38339,7 +38350,7 @@
       <c r="X291" s="10"/>
       <c r="Y291" s="10"/>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A292" s="34" t="s">
         <v>795</v>
       </c>
@@ -38380,7 +38391,7 @@
       <c r="X292" s="10"/>
       <c r="Y292" s="10"/>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A293" s="34" t="s">
         <v>796</v>
       </c>
@@ -38421,7 +38432,7 @@
       <c r="X293" s="10"/>
       <c r="Y293" s="10"/>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A294" s="34" t="s">
         <v>797</v>
       </c>
@@ -38462,7 +38473,7 @@
       <c r="X294" s="10"/>
       <c r="Y294" s="10"/>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A295" s="34" t="s">
         <v>798</v>
       </c>
@@ -38505,7 +38516,7 @@
       <c r="X295" s="10"/>
       <c r="Y295" s="10"/>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A296" s="34" t="s">
         <v>1454</v>
       </c>
@@ -38546,7 +38557,7 @@
       <c r="X296" s="10"/>
       <c r="Y296" s="10"/>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A297" s="34" t="s">
         <v>1456</v>
       </c>
@@ -38587,7 +38598,7 @@
       <c r="X297" s="10"/>
       <c r="Y297" s="10"/>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A298" s="34" t="s">
         <v>1458</v>
       </c>
@@ -38628,7 +38639,7 @@
       <c r="X298" s="10"/>
       <c r="Y298" s="10"/>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A299" s="34" t="s">
         <v>818</v>
       </c>
@@ -38669,7 +38680,7 @@
       <c r="X299" s="10"/>
       <c r="Y299" s="10"/>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A300" s="34" t="s">
         <v>821</v>
       </c>
@@ -38710,7 +38721,7 @@
       <c r="X300" s="10"/>
       <c r="Y300" s="10"/>
     </row>
-    <row r="301" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A301" s="34" t="s">
         <v>822</v>
       </c>
@@ -38751,7 +38762,7 @@
       <c r="X301" s="10"/>
       <c r="Y301" s="10"/>
     </row>
-    <row r="302" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A302" s="161" t="s">
         <v>1461</v>
       </c>
@@ -38794,7 +38805,7 @@
       <c r="X302" s="10"/>
       <c r="Y302" s="10"/>
     </row>
-    <row r="303" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A303" s="162" t="s">
         <v>1463</v>
       </c>
@@ -38835,7 +38846,7 @@
       <c r="X303" s="10"/>
       <c r="Y303" s="10"/>
     </row>
-    <row r="304" spans="1:25" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A304" s="162" t="s">
         <v>1465</v>
       </c>
@@ -38876,7 +38887,7 @@
       <c r="X304" s="10"/>
       <c r="Y304" s="10"/>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A305" s="162" t="s">
         <v>1467</v>
       </c>
@@ -38919,7 +38930,7 @@
       <c r="X305" s="10"/>
       <c r="Y305" s="10"/>
     </row>
-    <row r="306" spans="1:25" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A306" s="162" t="s">
         <v>1469</v>
       </c>
@@ -38960,7 +38971,7 @@
       <c r="X306" s="10"/>
       <c r="Y306" s="10"/>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A307" s="162" t="s">
         <v>1471</v>
       </c>
@@ -39001,7 +39012,7 @@
       <c r="X307" s="10"/>
       <c r="Y307" s="10"/>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A308" s="162" t="s">
         <v>1473</v>
       </c>
@@ -39042,7 +39053,7 @@
       <c r="X308" s="10"/>
       <c r="Y308" s="10"/>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A309" s="162" t="s">
         <v>1475</v>
       </c>
@@ -39083,7 +39094,7 @@
       <c r="X309" s="10"/>
       <c r="Y309" s="10"/>
     </row>
-    <row r="310" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A310" s="162" t="s">
         <v>1477</v>
       </c>
@@ -39124,7 +39135,7 @@
       <c r="X310" s="10"/>
       <c r="Y310" s="10"/>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A311" s="162" t="s">
         <v>1479</v>
       </c>
@@ -39165,7 +39176,7 @@
       <c r="X311" s="10"/>
       <c r="Y311" s="10"/>
     </row>
-    <row r="312" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" s="162" t="s">
         <v>1481</v>
       </c>
@@ -39206,7 +39217,7 @@
       <c r="X312" s="10"/>
       <c r="Y312" s="10"/>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A313" s="163" t="s">
         <v>1483</v>
       </c>
@@ -39249,7 +39260,7 @@
       <c r="X313" s="10"/>
       <c r="Y313" s="10"/>
     </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A314" s="34" t="s">
         <v>829</v>
       </c>
@@ -39290,7 +39301,7 @@
       <c r="X314" s="10"/>
       <c r="Y314" s="10"/>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A315" s="34" t="s">
         <v>830</v>
       </c>
@@ -39331,7 +39342,7 @@
       <c r="X315" s="10"/>
       <c r="Y315" s="10"/>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A316" s="34" t="s">
         <v>434</v>
       </c>
@@ -39372,7 +39383,7 @@
       <c r="X316" s="10"/>
       <c r="Y316" s="10"/>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A317" s="34" t="s">
         <v>832</v>
       </c>
@@ -39413,7 +39424,7 @@
       <c r="X317" s="10"/>
       <c r="Y317" s="10"/>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A318" s="34" t="s">
         <v>1487</v>
       </c>
@@ -39454,7 +39465,7 @@
       <c r="X318" s="10"/>
       <c r="Y318" s="10"/>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A319" s="34" t="s">
         <v>1489</v>
       </c>
@@ -39491,7 +39502,7 @@
       <c r="X319" s="10"/>
       <c r="Y319" s="10"/>
     </row>
-    <row r="320" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A320" s="34" t="s">
         <v>1491</v>
       </c>
@@ -39532,7 +39543,7 @@
       <c r="X320" s="10"/>
       <c r="Y320" s="10"/>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A321" s="34" t="s">
         <v>1493</v>
       </c>
@@ -39569,7 +39580,7 @@
       <c r="X321" s="10"/>
       <c r="Y321" s="10"/>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A322" s="34" t="s">
         <v>1495</v>
       </c>
@@ -39610,7 +39621,7 @@
       <c r="X322" s="10"/>
       <c r="Y322" s="10"/>
     </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A323" s="34" t="s">
         <v>1496</v>
       </c>
@@ -39647,7 +39658,7 @@
       <c r="X323" s="10"/>
       <c r="Y323" s="10"/>
     </row>
-    <row r="324" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A324" s="34" t="s">
         <v>1498</v>
       </c>
@@ -39688,7 +39699,7 @@
       <c r="X324" s="10"/>
       <c r="Y324" s="10"/>
     </row>
-    <row r="325" spans="1:25" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:25" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A325" s="91" t="s">
         <v>452</v>
       </c>
@@ -39721,7 +39732,7 @@
       <c r="X325" s="10"/>
       <c r="Y325" s="10"/>
     </row>
-    <row r="326" spans="1:25" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:25" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A326" s="36" t="s">
         <v>1502</v>
       </c>
@@ -39755,7 +39766,7 @@
       <c r="X326" s="10"/>
       <c r="Y326" s="10"/>
     </row>
-    <row r="327" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
       <c r="F327" s="10"/>
@@ -39782,7 +39793,7 @@
       <c r="X327" s="10"/>
       <c r="Y327" s="10"/>
     </row>
-    <row r="328" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
       <c r="F328" s="10"/>
@@ -39809,7 +39820,7 @@
       <c r="X328" s="10"/>
       <c r="Y328" s="10"/>
     </row>
-    <row r="329" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
       <c r="F329" s="10"/>
@@ -39836,7 +39847,7 @@
       <c r="X329" s="10"/>
       <c r="Y329" s="10"/>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
       <c r="F330" s="10"/>
@@ -39863,7 +39874,7 @@
       <c r="X330" s="10"/>
       <c r="Y330" s="10"/>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
       <c r="F331" s="10"/>
@@ -39890,7 +39901,7 @@
       <c r="X331" s="10"/>
       <c r="Y331" s="10"/>
     </row>
-    <row r="332" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
       <c r="F332" s="10"/>
@@ -39919,7 +39930,7 @@
       <c r="X332" s="10"/>
       <c r="Y332" s="10"/>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
       <c r="F333" s="10"/>
@@ -39946,7 +39957,7 @@
       <c r="X333" s="10"/>
       <c r="Y333" s="10"/>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
       <c r="F334" s="10"/>
@@ -39973,7 +39984,7 @@
       <c r="X334" s="10"/>
       <c r="Y334" s="10"/>
     </row>
-    <row r="335" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
       <c r="F335" s="10"/>
@@ -40000,7 +40011,7 @@
       <c r="X335" s="10"/>
       <c r="Y335" s="10"/>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
       <c r="F336" s="10"/>
@@ -40027,7 +40038,7 @@
       <c r="X336" s="10"/>
       <c r="Y336" s="10"/>
     </row>
-    <row r="337" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
       <c r="F337" s="10"/>
@@ -40054,7 +40065,7 @@
       <c r="X337" s="10"/>
       <c r="Y337" s="10"/>
     </row>
-    <row r="338" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
       <c r="F338" s="10"/>
@@ -40081,7 +40092,7 @@
       <c r="X338" s="10"/>
       <c r="Y338" s="10"/>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
       <c r="F339" s="10"/>
@@ -40108,7 +40119,7 @@
       <c r="X339" s="10"/>
       <c r="Y339" s="10"/>
     </row>
-    <row r="340" spans="1:25" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:25" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
       <c r="F340" s="10"/>
@@ -40135,7 +40146,7 @@
       <c r="X340" s="10"/>
       <c r="Y340" s="10"/>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
       <c r="F341" s="10"/>
@@ -40156,7 +40167,7 @@
       <c r="X341" s="10"/>
       <c r="Y341" s="10"/>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A342" s="2"/>
       <c r="C342" s="10"/>
       <c r="D342" s="10"/>
@@ -40178,7 +40189,7 @@
       <c r="X342" s="10"/>
       <c r="Y342" s="10"/>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A343" s="6"/>
       <c r="B343" s="8"/>
       <c r="C343" s="9"/>
@@ -40197,7 +40208,7 @@
       <c r="S343" s="8"/>
       <c r="U343" s="8"/>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>2194</v>
       </c>
@@ -40205,7 +40216,7 @@
       <c r="U344" s="1"/>
       <c r="V344" s="2"/>
     </row>
-    <row r="345" spans="1:25" ht="174" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:25" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>2196</v>
       </c>
@@ -40233,7 +40244,7 @@
       <c r="X345" s="10"/>
       <c r="Y345" s="10"/>
     </row>
-    <row r="346" spans="1:25" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A346" s="2"/>
       <c r="C346" s="289" t="s">
         <v>2198</v>
@@ -40257,7 +40268,7 @@
       <c r="X346" s="10"/>
       <c r="Y346" s="10"/>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A347" s="2"/>
       <c r="C347" s="10"/>
       <c r="D347" s="10"/>
@@ -40279,7 +40290,7 @@
       <c r="X347" s="10"/>
       <c r="Y347" s="10"/>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A348" s="2"/>
       <c r="C348" s="10"/>
       <c r="D348" s="10"/>
@@ -40301,7 +40312,7 @@
       <c r="X348" s="10"/>
       <c r="Y348" s="10"/>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A349" s="2"/>
       <c r="C349" s="10"/>
       <c r="D349" s="10"/>
@@ -40323,7 +40334,7 @@
       <c r="X349" s="10"/>
       <c r="Y349" s="10"/>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A350" s="2"/>
       <c r="C350" s="10"/>
       <c r="D350" s="10"/>
@@ -40345,7 +40356,7 @@
       <c r="X350" s="10"/>
       <c r="Y350" s="10"/>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A351" s="6"/>
       <c r="B351" s="8"/>
       <c r="C351" s="9"/>
@@ -40364,7 +40375,7 @@
       <c r="S351" s="8"/>
       <c r="U351" s="8"/>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>148</v>
       </c>
@@ -40375,7 +40386,7 @@
       <c r="U352" s="1"/>
       <c r="V352" s="2"/>
     </row>
-    <row r="353" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B353" s="1"/>
       <c r="F353" s="4" t="s">
         <v>155</v>
@@ -40393,7 +40404,7 @@
       </c>
       <c r="V353" s="2"/>
     </row>
-    <row r="354" spans="1:25" ht="232.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:25" ht="231" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" s="189" t="s">
         <v>159</v>
       </c>
@@ -40450,7 +40461,7 @@
       <c r="X354" s="217"/>
       <c r="Y354" s="10"/>
     </row>
-    <row r="355" spans="1:25" ht="203" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:25" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A355" s="220" t="s">
         <v>1871</v>
       </c>
@@ -40492,7 +40503,7 @@
       <c r="U355" s="1"/>
       <c r="Y355" s="10"/>
     </row>
-    <row r="356" spans="1:25" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:25" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" s="129" t="s">
         <v>1511</v>
       </c>
@@ -40532,7 +40543,7 @@
       <c r="U356" s="1"/>
       <c r="Y356" s="10"/>
     </row>
-    <row r="357" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A357" s="263" t="s">
         <v>1512</v>
       </c>
@@ -40569,7 +40580,7 @@
       <c r="U357" s="1"/>
       <c r="Y357" s="10"/>
     </row>
-    <row r="358" spans="1:25" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:25" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A358" s="263" t="s">
         <v>1513</v>
       </c>
@@ -40611,7 +40622,7 @@
       <c r="X358" s="10"/>
       <c r="Y358" s="10"/>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A359" s="195" t="s">
         <v>1514</v>
       </c>
@@ -40651,7 +40662,7 @@
       <c r="X359" s="10"/>
       <c r="Y359" s="10"/>
     </row>
-    <row r="360" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A360" s="263" t="s">
         <v>210</v>
       </c>
@@ -40691,7 +40702,7 @@
       <c r="X360" s="10"/>
       <c r="Y360" s="10"/>
     </row>
-    <row r="361" spans="1:25" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:25" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A361" s="263" t="s">
         <v>212</v>
       </c>
@@ -40733,7 +40744,7 @@
       <c r="X361" s="10"/>
       <c r="Y361" s="10"/>
     </row>
-    <row r="362" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A362" s="192" t="s">
         <v>1518</v>
       </c>
@@ -40773,7 +40784,7 @@
       <c r="X362" s="10"/>
       <c r="Y362" s="10"/>
     </row>
-    <row r="363" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A363" s="34" t="s">
         <v>1823</v>
       </c>
@@ -40811,7 +40822,7 @@
       <c r="X363" s="10"/>
       <c r="Y363" s="10"/>
     </row>
-    <row r="364" spans="1:25" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:25" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" s="145" t="s">
         <v>1794</v>
       </c>
@@ -40851,7 +40862,7 @@
       <c r="X364" s="10"/>
       <c r="Y364" s="10"/>
     </row>
-    <row r="365" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="145" t="s">
         <v>1796</v>
       </c>
@@ -40882,7 +40893,7 @@
       <c r="X365" s="10"/>
       <c r="Y365" s="10"/>
     </row>
-    <row r="366" spans="1:25" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:25" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="263" t="s">
         <v>1520</v>
       </c>
@@ -40903,7 +40914,7 @@
       <c r="X366" s="10"/>
       <c r="Y366" s="10"/>
     </row>
-    <row r="367" spans="1:25" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:25" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" s="263" t="s">
         <v>1521</v>
       </c>
@@ -40937,7 +40948,7 @@
       <c r="X367" s="10"/>
       <c r="Y367" s="10"/>
     </row>
-    <row r="368" spans="1:25" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:25" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A368" s="263" t="s">
         <v>428</v>
       </c>
@@ -40960,7 +40971,7 @@
       <c r="X368" s="10"/>
       <c r="Y368" s="10"/>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A369" s="145" t="s">
         <v>262</v>
       </c>
@@ -40981,7 +40992,7 @@
       <c r="X369" s="10"/>
       <c r="Y369" s="10"/>
     </row>
-    <row r="370" spans="1:25" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A370" s="192" t="s">
         <v>1522</v>
       </c>
@@ -41007,7 +41018,7 @@
       <c r="X370" s="10"/>
       <c r="Y370" s="10"/>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A371" s="145" t="s">
         <v>1800</v>
       </c>
@@ -41033,7 +41044,7 @@
       <c r="X371" s="10"/>
       <c r="Y371" s="10"/>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A372" s="145" t="s">
         <v>1523</v>
       </c>
@@ -41059,7 +41070,7 @@
       <c r="X372" s="10"/>
       <c r="Y372" s="10"/>
     </row>
-    <row r="373" spans="1:25" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A373" s="266" t="s">
         <v>1532</v>
       </c>
@@ -41087,7 +41098,7 @@
       <c r="X373" s="10"/>
       <c r="Y373" s="10"/>
     </row>
-    <row r="374" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A374" s="263" t="s">
         <v>1533</v>
       </c>
@@ -41115,7 +41126,7 @@
       <c r="X374" s="10"/>
       <c r="Y374" s="10"/>
     </row>
-    <row r="375" spans="1:25" ht="145" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:25" ht="144" x14ac:dyDescent="0.3">
       <c r="A375" s="263" t="s">
         <v>1803</v>
       </c>
@@ -41143,7 +41154,7 @@
       <c r="X375" s="10"/>
       <c r="Y375" s="10"/>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A376" s="145" t="s">
         <v>1804</v>
       </c>
@@ -41169,7 +41180,7 @@
       <c r="X376" s="10"/>
       <c r="Y376" s="10"/>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A377" s="199" t="s">
         <v>1807</v>
       </c>
@@ -41195,7 +41206,7 @@
       <c r="X377" s="10"/>
       <c r="Y377" s="10"/>
     </row>
-    <row r="378" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A378" s="145" t="s">
         <v>1809</v>
       </c>
@@ -41221,7 +41232,7 @@
       <c r="X378" s="10"/>
       <c r="Y378" s="10"/>
     </row>
-    <row r="379" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A379" s="192" t="s">
         <v>1536</v>
       </c>
@@ -41247,7 +41258,7 @@
       <c r="X379" s="10"/>
       <c r="Y379" s="10"/>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A380" s="192" t="s">
         <v>249</v>
       </c>
@@ -41273,7 +41284,7 @@
       <c r="X380" s="10"/>
       <c r="Y380" s="10"/>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A381" s="145" t="s">
         <v>1538</v>
       </c>
@@ -41299,7 +41310,7 @@
       <c r="X381" s="10"/>
       <c r="Y381" s="10"/>
     </row>
-    <row r="382" spans="1:25" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A382" s="192" t="s">
         <v>1811</v>
       </c>
@@ -41325,7 +41336,7 @@
       <c r="X382" s="10"/>
       <c r="Y382" s="10"/>
     </row>
-    <row r="383" spans="1:25" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:25" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A383" s="263" t="s">
         <v>252</v>
       </c>
@@ -41353,7 +41364,7 @@
       <c r="X383" s="10"/>
       <c r="Y383" s="10"/>
     </row>
-    <row r="384" spans="1:25" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A384" s="263" t="s">
         <v>1540</v>
       </c>
@@ -41381,7 +41392,7 @@
       <c r="X384" s="10"/>
       <c r="Y384" s="10"/>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A385" s="91" t="s">
         <v>452</v>
       </c>
@@ -41405,7 +41416,7 @@
       <c r="X385" s="10"/>
       <c r="Y385" s="10"/>
     </row>
-    <row r="386" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" s="65" t="s">
         <v>1502</v>
       </c>
@@ -41431,7 +41442,7 @@
       <c r="X386" s="10"/>
       <c r="Y386" s="10"/>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C387" s="10"/>
       <c r="D387" s="10"/>
       <c r="G387" s="1"/>
@@ -41449,7 +41460,7 @@
       <c r="X387" s="10"/>
       <c r="Y387" s="10"/>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A388" s="6"/>
       <c r="B388" s="8"/>
       <c r="C388" s="9"/>
@@ -41468,7 +41479,7 @@
       <c r="S388" s="8"/>
       <c r="U388" s="8"/>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>1873</v>
       </c>
@@ -41476,7 +41487,7 @@
       <c r="U389" s="1"/>
       <c r="V389" s="2"/>
     </row>
-    <row r="390" spans="1:25" ht="29" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>1874</v>
       </c>
@@ -41501,7 +41512,7 @@
       <c r="X390" s="10"/>
       <c r="Y390" s="10"/>
     </row>
-    <row r="391" spans="1:25" ht="58" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>1876</v>
       </c>
@@ -41527,7 +41538,7 @@
       <c r="X391" s="10"/>
       <c r="Y391" s="10"/>
     </row>
-    <row r="392" spans="1:25" ht="116" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:25" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>1878</v>
       </c>
@@ -41553,7 +41564,7 @@
       <c r="X392" s="10"/>
       <c r="Y392" s="10"/>
     </row>
-    <row r="393" spans="1:25" ht="87" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>1880</v>
       </c>
@@ -41581,7 +41592,7 @@
       <c r="X393" s="10"/>
       <c r="Y393" s="10"/>
     </row>
-    <row r="394" spans="1:25" ht="174" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:25" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>2004</v>
       </c>
@@ -41607,7 +41618,7 @@
       <c r="X394" s="10"/>
       <c r="Y394" s="10"/>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>1960</v>
       </c>
@@ -41630,7 +41641,7 @@
       <c r="X395" s="10"/>
       <c r="Y395" s="10"/>
     </row>
-    <row r="396" spans="1:25" ht="58" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>1958</v>
       </c>
@@ -41655,7 +41666,7 @@
       <c r="X396" s="10"/>
       <c r="Y396" s="10"/>
     </row>
-    <row r="397" spans="1:25" ht="116" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:25" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>2003</v>
       </c>
@@ -41680,7 +41691,7 @@
       <c r="X397" s="10"/>
       <c r="Y397" s="10"/>
     </row>
-    <row r="398" spans="1:25" ht="87" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>2005</v>
       </c>
@@ -41706,7 +41717,7 @@
       <c r="X398" s="10"/>
       <c r="Y398" s="10"/>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C399" s="246"/>
       <c r="D399" s="10"/>
       <c r="F399" s="10"/>
@@ -41727,7 +41738,7 @@
       <c r="X399" s="10"/>
       <c r="Y399" s="10"/>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A400" s="6"/>
       <c r="B400" s="8"/>
       <c r="C400" s="9"/>
@@ -41746,7 +41757,7 @@
       <c r="S400" s="8"/>
       <c r="U400" s="8"/>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>173</v>
       </c>
@@ -41754,7 +41765,7 @@
       <c r="U401" s="1"/>
       <c r="V401" s="2"/>
     </row>
-    <row r="402" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
       <c r="F402" s="4" t="s">
@@ -41773,7 +41784,7 @@
       </c>
       <c r="V402" s="2"/>
     </row>
-    <row r="403" spans="1:25" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:25" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A403" s="78" t="s">
         <v>177</v>
       </c>
@@ -41818,7 +41829,7 @@
       <c r="X403" s="10"/>
       <c r="Y403" s="10"/>
     </row>
-    <row r="404" spans="1:25" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:25" ht="216" x14ac:dyDescent="0.3">
       <c r="A404" s="34"/>
       <c r="B404" s="79" t="s">
         <v>180</v>
@@ -41848,7 +41859,7 @@
       </c>
       <c r="N404" s="35"/>
     </row>
-    <row r="405" spans="1:25" ht="116" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:25" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A405" s="34"/>
       <c r="B405" s="79" t="s">
         <v>181</v>
@@ -41880,7 +41891,7 @@
       </c>
       <c r="N405" s="35"/>
     </row>
-    <row r="406" spans="1:25" ht="160" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:25" ht="159" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" s="36"/>
       <c r="B406" s="80" t="s">
         <v>182</v>
@@ -41910,7 +41921,7 @@
       </c>
       <c r="N406" s="35"/>
     </row>
-    <row r="407" spans="1:25" ht="116" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:25" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
       <c r="F407" s="19" t="s">
@@ -41934,7 +41945,7 @@
       </c>
       <c r="N407" s="35"/>
     </row>
-    <row r="408" spans="1:25" ht="58" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
       <c r="F408" s="19"/>
@@ -41954,7 +41965,7 @@
       </c>
       <c r="N408" s="35"/>
     </row>
-    <row r="409" spans="1:25" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:25" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F409" s="36" t="s">
         <v>196</v>
       </c>
@@ -41974,15 +41985,15 @@
       </c>
       <c r="N409" s="37"/>
     </row>
-    <row r="410" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
     </row>
-    <row r="411" spans="1:25" ht="93.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:25" ht="93.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C411" s="264"/>
     </row>
-    <row r="412" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="413" spans="1:25" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="413" spans="1:25" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A413" s="89" t="s">
         <v>174</v>
       </c>
@@ -42020,7 +42031,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="414" spans="1:25" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A414" s="19" t="s">
         <v>188</v>
       </c>
@@ -42052,7 +42063,7 @@
       </c>
       <c r="N414" s="35"/>
     </row>
-    <row r="415" spans="1:25" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A415" s="264"/>
       <c r="B415" s="79" t="s">
         <v>186</v>
@@ -42084,7 +42095,7 @@
       </c>
       <c r="N415" s="35"/>
     </row>
-    <row r="416" spans="1:25" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A416" s="171" t="s">
         <v>1511</v>
       </c>
@@ -42111,7 +42122,7 @@
       </c>
       <c r="N416" s="35"/>
     </row>
-    <row r="417" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A417" s="173" t="s">
         <v>1512</v>
       </c>
@@ -42139,7 +42150,7 @@
       </c>
       <c r="N417" s="35"/>
     </row>
-    <row r="418" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A418" s="173" t="s">
         <v>1513</v>
       </c>
@@ -42168,7 +42179,7 @@
       </c>
       <c r="N418" s="35"/>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A419" s="173" t="s">
         <v>1514</v>
       </c>
@@ -42200,7 +42211,7 @@
       </c>
       <c r="N419" s="35"/>
     </row>
-    <row r="420" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A420" s="173" t="s">
         <v>1515</v>
       </c>
@@ -42232,7 +42243,7 @@
       </c>
       <c r="N420" s="35"/>
     </row>
-    <row r="421" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:14" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="175" t="s">
         <v>1516</v>
       </c>
@@ -42264,7 +42275,7 @@
       </c>
       <c r="N421" s="35"/>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A422" s="81" t="s">
         <v>210</v>
       </c>
@@ -42296,7 +42307,7 @@
       </c>
       <c r="N422" s="35"/>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A423" s="81" t="s">
         <v>212</v>
       </c>
@@ -42328,7 +42339,7 @@
       </c>
       <c r="N423" s="35"/>
     </row>
-    <row r="424" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:14" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="50" t="s">
         <v>1518</v>
       </c>
@@ -42360,7 +42371,7 @@
       </c>
       <c r="N424" s="35"/>
     </row>
-    <row r="425" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:14" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="81" t="s">
         <v>213</v>
       </c>
@@ -42392,7 +42403,7 @@
       </c>
       <c r="N425" s="35"/>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A426" s="82" t="s">
         <v>198</v>
       </c>
@@ -42424,7 +42435,7 @@
       </c>
       <c r="N426" s="35"/>
     </row>
-    <row r="427" spans="1:14" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:14" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A427" s="82" t="s">
         <v>1520</v>
       </c>
@@ -42458,7 +42469,7 @@
       </c>
       <c r="N427" s="35"/>
     </row>
-    <row r="428" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A428" s="81" t="s">
         <v>218</v>
       </c>
@@ -42490,7 +42501,7 @@
       </c>
       <c r="N428" s="35"/>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A429" s="81" t="s">
         <v>220</v>
       </c>
@@ -42512,7 +42523,7 @@
       </c>
       <c r="N429" s="35"/>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A430" s="19" t="s">
         <v>1521</v>
       </c>
@@ -42536,7 +42547,7 @@
       </c>
       <c r="N430" s="35"/>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A431" s="19" t="s">
         <v>1522</v>
       </c>
@@ -42560,7 +42571,7 @@
       </c>
       <c r="N431" s="35"/>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A432" s="81" t="s">
         <v>1523</v>
       </c>
@@ -42582,7 +42593,7 @@
       </c>
       <c r="N432" s="35"/>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A433" s="171" t="s">
         <v>1524</v>
       </c>
@@ -42604,7 +42615,7 @@
       </c>
       <c r="N433" s="35"/>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A434" s="173" t="s">
         <v>1525</v>
       </c>
@@ -42626,7 +42637,7 @@
       </c>
       <c r="N434" s="35"/>
     </row>
-    <row r="435" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:14" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="175" t="s">
         <v>1526</v>
       </c>
@@ -42648,7 +42659,7 @@
       </c>
       <c r="N435" s="35"/>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A436" s="82" t="s">
         <v>229</v>
       </c>
@@ -42670,7 +42681,7 @@
       </c>
       <c r="N436" s="35"/>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A437" s="82" t="s">
         <v>230</v>
       </c>
@@ -42692,7 +42703,7 @@
       </c>
       <c r="N437" s="35"/>
     </row>
-    <row r="438" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:14" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="82" t="s">
         <v>231</v>
       </c>
@@ -42714,7 +42725,7 @@
       </c>
       <c r="N438" s="35"/>
     </row>
-    <row r="439" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="179" t="s">
         <v>232</v>
       </c>
@@ -42736,7 +42747,7 @@
       </c>
       <c r="N439" s="35"/>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A440" s="180" t="s">
         <v>234</v>
       </c>
@@ -42758,7 +42769,7 @@
       </c>
       <c r="N440" s="35"/>
     </row>
-    <row r="441" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A441" s="181" t="s">
         <v>235</v>
       </c>
@@ -42780,7 +42791,7 @@
       </c>
       <c r="N441" s="37"/>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A442" s="81" t="s">
         <v>236</v>
       </c>
@@ -42792,7 +42803,7 @@
       </c>
       <c r="D442" s="35"/>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A443" s="182" t="s">
         <v>1531</v>
       </c>
@@ -42804,7 +42815,7 @@
       </c>
       <c r="D443" s="35"/>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A444" s="179" t="s">
         <v>239</v>
       </c>
@@ -42816,7 +42827,7 @@
       </c>
       <c r="D444" s="139"/>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A445" s="180" t="s">
         <v>1532</v>
       </c>
@@ -42828,7 +42839,7 @@
       </c>
       <c r="D445" s="140"/>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A446" s="183" t="s">
         <v>1533</v>
       </c>
@@ -42840,7 +42851,7 @@
       </c>
       <c r="D446" s="140"/>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A447" s="180" t="s">
         <v>242</v>
       </c>
@@ -42852,7 +42863,7 @@
       </c>
       <c r="D447" s="140"/>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A448" s="183" t="s">
         <v>1534</v>
       </c>
@@ -42864,7 +42875,7 @@
       </c>
       <c r="D448" s="140"/>
     </row>
-    <row r="449" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A449" s="180" t="s">
         <v>245</v>
       </c>
@@ -42876,7 +42887,7 @@
       </c>
       <c r="D449" s="140"/>
     </row>
-    <row r="450" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A450" s="184" t="s">
         <v>1535</v>
       </c>
@@ -42888,7 +42899,7 @@
       </c>
       <c r="D450" s="141"/>
     </row>
-    <row r="451" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:22" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="19" t="s">
         <v>1536</v>
       </c>
@@ -42900,7 +42911,7 @@
       </c>
       <c r="D451" s="35"/>
     </row>
-    <row r="452" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A452" s="82" t="s">
         <v>249</v>
       </c>
@@ -42912,7 +42923,7 @@
       </c>
       <c r="D452" s="35"/>
     </row>
-    <row r="453" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:22" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="81" t="s">
         <v>1538</v>
       </c>
@@ -42924,7 +42935,7 @@
       </c>
       <c r="D453" s="35"/>
     </row>
-    <row r="454" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="110" t="s">
         <v>252</v>
       </c>
@@ -42936,7 +42947,7 @@
       </c>
       <c r="D454" s="35"/>
     </row>
-    <row r="455" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A455" s="109" t="s">
         <v>1540</v>
       </c>
@@ -42948,7 +42959,7 @@
       </c>
       <c r="D455" s="37"/>
     </row>
-    <row r="459" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A459" s="6"/>
       <c r="B459" s="8"/>
       <c r="C459" s="9"/>
@@ -42967,7 +42978,7 @@
       <c r="S459" s="8"/>
       <c r="U459" s="8"/>
     </row>
-    <row r="460" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>1889</v>
       </c>
@@ -42975,7 +42986,7 @@
       <c r="U460" s="1"/>
       <c r="V460" s="2"/>
     </row>
-    <row r="461" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A461" s="223" t="s">
         <v>1927</v>
       </c>
@@ -42996,7 +43007,7 @@
       </c>
       <c r="V461" s="2"/>
     </row>
-    <row r="462" spans="1:22" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:22" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A462" s="230" t="s">
         <v>1928</v>
       </c>
@@ -43030,7 +43041,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="463" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A463" s="227" t="s">
         <v>1890</v>
       </c>
@@ -43045,7 +43056,7 @@
       <c r="H463"/>
       <c r="I463" s="2"/>
     </row>
-    <row r="464" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A464" s="228"/>
       <c r="B464" s="222"/>
       <c r="C464" s="290" t="s">
@@ -43056,7 +43067,7 @@
       <c r="G464"/>
       <c r="H464"/>
     </row>
-    <row r="465" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A465" s="34"/>
       <c r="B465" s="2" t="s">
         <v>1891</v>
@@ -43066,7 +43077,7 @@
       </c>
       <c r="D465" s="35"/>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A466" s="34" t="s">
         <v>210</v>
       </c>
@@ -43078,7 +43089,7 @@
       </c>
       <c r="D466" s="35"/>
     </row>
-    <row r="467" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A467" s="34" t="s">
         <v>212</v>
       </c>
@@ -43090,7 +43101,7 @@
       </c>
       <c r="D467" s="35"/>
     </row>
-    <row r="468" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A468" s="34" t="s">
         <v>1896</v>
       </c>
@@ -43102,7 +43113,7 @@
       </c>
       <c r="D468" s="35"/>
     </row>
-    <row r="469" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A469" s="34" t="s">
         <v>1898</v>
       </c>
@@ -43114,7 +43125,7 @@
       </c>
       <c r="D469" s="35"/>
     </row>
-    <row r="470" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A470" s="34" t="s">
         <v>1900</v>
       </c>
@@ -43126,7 +43137,7 @@
       </c>
       <c r="D470" s="35"/>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A471" s="34" t="s">
         <v>1902</v>
       </c>
@@ -43138,7 +43149,7 @@
       </c>
       <c r="D471" s="35"/>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A472" s="34" t="s">
         <v>1904</v>
       </c>
@@ -43150,7 +43161,7 @@
       </c>
       <c r="D472" s="35"/>
     </row>
-    <row r="473" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A473" s="34" t="s">
         <v>1907</v>
       </c>
@@ -43164,7 +43175,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A474" s="34" t="s">
         <v>1909</v>
       </c>
@@ -43176,7 +43187,7 @@
       </c>
       <c r="D474" s="35"/>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A475" s="34" t="s">
         <v>428</v>
       </c>
@@ -43188,7 +43199,7 @@
       </c>
       <c r="D475" s="35"/>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A476" s="34" t="s">
         <v>1913</v>
       </c>
@@ -43200,7 +43211,7 @@
       </c>
       <c r="D476" s="35"/>
     </row>
-    <row r="477" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A477" s="34" t="s">
         <v>1915</v>
       </c>
@@ -43212,7 +43223,7 @@
       </c>
       <c r="D477" s="35"/>
     </row>
-    <row r="478" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A478" s="229" t="s">
         <v>1917</v>
       </c>
@@ -43226,7 +43237,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" s="34" t="s">
         <v>1919</v>
       </c>
@@ -43238,7 +43249,7 @@
       </c>
       <c r="D479" s="35"/>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A480" s="34" t="s">
         <v>1921</v>
       </c>
@@ -43250,7 +43261,7 @@
       </c>
       <c r="D480" s="35"/>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A481" s="34" t="s">
         <v>249</v>
       </c>
@@ -43262,7 +43273,7 @@
       </c>
       <c r="D481" s="35"/>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A482" s="34" t="s">
         <v>1925</v>
       </c>
@@ -43274,7 +43285,7 @@
       </c>
       <c r="D482" s="35"/>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A483" s="234" t="s">
         <v>1935</v>
       </c>
@@ -43284,7 +43295,7 @@
       </c>
       <c r="D483" s="112"/>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" s="229" t="s">
         <v>1936</v>
       </c>
@@ -43293,7 +43304,7 @@
       </c>
       <c r="D484" s="35"/>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" s="229" t="s">
         <v>1938</v>
       </c>
@@ -43302,7 +43313,7 @@
       </c>
       <c r="D485" s="35"/>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" s="229" t="s">
         <v>1940</v>
       </c>
@@ -43311,7 +43322,7 @@
       </c>
       <c r="D486" s="35"/>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" s="229" t="s">
         <v>1942</v>
       </c>
@@ -43320,7 +43331,7 @@
       </c>
       <c r="D487" s="35"/>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A488" s="229" t="s">
         <v>1944</v>
       </c>
@@ -43329,7 +43340,7 @@
       </c>
       <c r="D488" s="35"/>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" s="229" t="s">
         <v>1913</v>
       </c>
@@ -43338,7 +43349,7 @@
       </c>
       <c r="D489" s="35"/>
     </row>
-    <row r="490" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A490" s="235" t="s">
         <v>1925</v>
       </c>
@@ -43348,7 +43359,7 @@
       </c>
       <c r="D490" s="37"/>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>1954</v>
       </c>
@@ -43356,12 +43367,12 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="497" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>1955</v>
       </c>
     </row>
-    <row r="501" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A501" s="6"/>
       <c r="B501" s="8"/>
       <c r="C501" s="9"/>
@@ -43380,7 +43391,7 @@
       <c r="S501" s="8"/>
       <c r="U501" s="8"/>
     </row>
-    <row r="502" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>2145</v>
       </c>
@@ -43388,7 +43399,7 @@
       <c r="U502" s="1"/>
       <c r="V502" s="2"/>
     </row>
-    <row r="503" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A503" s="223" t="s">
         <v>1927</v>
       </c>
@@ -43409,7 +43420,7 @@
       </c>
       <c r="V503" s="2"/>
     </row>
-    <row r="504" spans="1:22" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:22" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A504" s="1" t="s">
         <v>1961</v>
       </c>
@@ -43420,7 +43431,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="505" spans="1:22" ht="174" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A505" s="89" t="s">
         <v>1962</v>
       </c>
@@ -43434,7 +43445,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="506" spans="1:22" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:22" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A506" s="34"/>
       <c r="C506" s="243" t="s">
         <v>1966</v>
@@ -43443,7 +43454,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="507" spans="1:22" ht="174" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A507" s="34"/>
       <c r="C507" s="243" t="s">
         <v>1967</v>
@@ -43476,7 +43487,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="508" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A508" s="81" t="s">
         <v>1512</v>
       </c>
@@ -43503,7 +43514,7 @@
       </c>
       <c r="N508" s="35"/>
     </row>
-    <row r="509" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A509" s="81" t="s">
         <v>210</v>
       </c>
@@ -43530,7 +43541,7 @@
       </c>
       <c r="N509" s="35"/>
     </row>
-    <row r="510" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A510" s="81" t="s">
         <v>212</v>
       </c>
@@ -43557,7 +43568,7 @@
       </c>
       <c r="N510" s="35"/>
     </row>
-    <row r="511" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A511" s="81" t="s">
         <v>1518</v>
       </c>
@@ -43584,7 +43595,7 @@
       </c>
       <c r="N511" s="35"/>
     </row>
-    <row r="512" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A512" s="81" t="s">
         <v>428</v>
       </c>
@@ -43611,7 +43622,7 @@
       </c>
       <c r="N512" s="35"/>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A513" s="81" t="s">
         <v>262</v>
       </c>
@@ -43638,7 +43649,7 @@
       </c>
       <c r="N513" s="35"/>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A514" s="81" t="s">
         <v>1533</v>
       </c>
@@ -43665,7 +43676,7 @@
       </c>
       <c r="N514" s="35"/>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A515" s="81" t="s">
         <v>249</v>
       </c>
@@ -43692,7 +43703,7 @@
       </c>
       <c r="N515" s="35"/>
     </row>
-    <row r="516" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A516" s="273" t="s">
         <v>1538</v>
       </c>
@@ -43719,7 +43730,7 @@
       </c>
       <c r="N516" s="35"/>
     </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F517" s="34" t="s">
         <v>2123</v>
       </c>
@@ -43736,7 +43747,7 @@
       </c>
       <c r="N517" s="35"/>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F518" s="34" t="s">
         <v>2126</v>
       </c>
@@ -43753,7 +43764,7 @@
       </c>
       <c r="N518" s="35"/>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F519" s="34" t="s">
         <v>2128</v>
       </c>
@@ -43770,7 +43781,7 @@
       </c>
       <c r="N519" s="35"/>
     </row>
-    <row r="520" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F520" s="34" t="s">
         <v>2130</v>
       </c>
@@ -43788,7 +43799,7 @@
       </c>
       <c r="N520" s="37"/>
     </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F521" s="34" t="s">
         <v>428</v>
       </c>
@@ -43800,7 +43811,7 @@
       </c>
       <c r="I521" s="35"/>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F522" s="34" t="s">
         <v>262</v>
       </c>
@@ -43812,7 +43823,7 @@
       </c>
       <c r="I522" s="35"/>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F523" s="34" t="s">
         <v>2117</v>
       </c>
@@ -43824,7 +43835,7 @@
       </c>
       <c r="I523" s="35"/>
     </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F524" s="34" t="s">
         <v>2132</v>
       </c>
@@ -43836,7 +43847,7 @@
       </c>
       <c r="I524" s="35"/>
     </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F525" s="34" t="s">
         <v>234</v>
       </c>
@@ -43848,7 +43859,7 @@
       </c>
       <c r="I525" s="35"/>
     </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F526" s="34" t="s">
         <v>235</v>
       </c>
@@ -43860,7 +43871,7 @@
       </c>
       <c r="I526" s="35"/>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F527" s="34" t="s">
         <v>1533</v>
       </c>
@@ -43872,7 +43883,7 @@
       </c>
       <c r="I527" s="35"/>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F528" s="34" t="s">
         <v>249</v>
       </c>
@@ -43884,7 +43895,7 @@
       </c>
       <c r="I528" s="35"/>
     </row>
-    <row r="529" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:22" x14ac:dyDescent="0.3">
       <c r="F529" s="34" t="s">
         <v>1538</v>
       </c>
@@ -43896,7 +43907,7 @@
       </c>
       <c r="I529" s="35"/>
     </row>
-    <row r="530" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:22" x14ac:dyDescent="0.3">
       <c r="F530" s="34" t="s">
         <v>2136</v>
       </c>
@@ -43908,7 +43919,7 @@
       </c>
       <c r="I530" s="35"/>
     </row>
-    <row r="531" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:22" x14ac:dyDescent="0.3">
       <c r="F531" s="34" t="s">
         <v>2138</v>
       </c>
@@ -43920,7 +43931,7 @@
       </c>
       <c r="I531" s="35"/>
     </row>
-    <row r="532" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:22" x14ac:dyDescent="0.3">
       <c r="F532" s="34" t="s">
         <v>2140</v>
       </c>
@@ -43932,7 +43943,7 @@
       </c>
       <c r="I532" s="35"/>
     </row>
-    <row r="533" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F533" s="36" t="s">
         <v>2142</v>
       </c>
@@ -43944,7 +43955,7 @@
       </c>
       <c r="I533" s="37"/>
     </row>
-    <row r="536" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A536" s="6"/>
       <c r="B536" s="8"/>
       <c r="C536" s="9"/>
@@ -43963,7 +43974,7 @@
       <c r="S536" s="8"/>
       <c r="U536" s="8"/>
     </row>
-    <row r="537" spans="1:22" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:22" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A537" s="1" t="s">
         <v>2144</v>
       </c>
@@ -43971,7 +43982,7 @@
       <c r="U537" s="1"/>
       <c r="V537" s="2"/>
     </row>
-    <row r="538" spans="1:22" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A538" s="88" t="s">
         <v>1975</v>
       </c>
@@ -43983,7 +43994,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="539" spans="1:22" ht="203" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A539" s="34"/>
       <c r="B539" s="2" t="s">
         <v>1982</v>
@@ -43995,7 +44006,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="540" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A540" s="34"/>
       <c r="B540" s="2" t="s">
         <v>1983</v>
@@ -44007,7 +44018,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="541" spans="1:22" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:22" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A541" s="36"/>
       <c r="B541" s="22" t="s">
         <v>1986</v>
@@ -44019,7 +44030,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="542" spans="1:22" ht="145" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A542" s="277" t="s">
         <v>2087</v>
       </c>
@@ -44033,7 +44044,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="543" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A543" s="34" t="s">
         <v>2090</v>
       </c>
@@ -44044,7 +44055,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="544" spans="1:22" ht="174" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A544" s="19" t="s">
         <v>2092</v>
       </c>
@@ -44058,7 +44069,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="545" spans="1:4" ht="145.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:4" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A545" s="36"/>
       <c r="B545" s="22" t="s">
         <v>2097</v>
@@ -44083,44 +44094,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="73.81640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="43.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.90625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="66.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.81640625" style="11" customWidth="1"/>
-    <col min="11" max="11" width="39.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="92.453125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="60.54296875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.81640625" style="11" customWidth="1"/>
-    <col min="16" max="16" width="56.81640625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="54.36328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="58.81640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.81640625" style="12"/>
-    <col min="21" max="21" width="67.81640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.36328125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.36328125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6328125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.1796875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="125.08984375" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="1" width="48.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="58.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="73.77734375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="66.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="11" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="92.44140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="60.5546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="11" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="54.33203125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="58.77734375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="12"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="125.109375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
@@ -44139,7 +44150,7 @@
       <c r="S2" s="8"/>
       <c r="U2" s="8"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -44147,7 +44158,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -44167,7 +44178,7 @@
       </c>
       <c r="V4" s="2"/>
     </row>
-    <row r="5" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A5" s="89" t="s">
         <v>2170</v>
       </c>
@@ -44179,21 +44190,21 @@
       </c>
       <c r="D5" s="43"/>
     </row>
-    <row r="6" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="34"/>
       <c r="C6" s="281" t="s">
         <v>2167</v>
       </c>
       <c r="D6" s="35"/>
     </row>
-    <row r="7" spans="1:22" ht="174" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34"/>
       <c r="C7" s="281" t="s">
         <v>2168</v>
       </c>
       <c r="D7" s="35"/>
     </row>
-    <row r="8" spans="1:22" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="36"/>
       <c r="B8" s="22"/>
       <c r="C8" s="282" t="s">
@@ -44201,8 +44212,8 @@
       </c>
       <c r="D8" s="37"/>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="89" t="s">
         <v>2172</v>
       </c>
@@ -44214,28 +44225,28 @@
       </c>
       <c r="D10" s="43"/>
     </row>
-    <row r="11" spans="1:22" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A11" s="34"/>
       <c r="C11" s="281" t="s">
         <v>2178</v>
       </c>
       <c r="D11" s="35"/>
     </row>
-    <row r="12" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A12" s="34"/>
       <c r="C12" s="281" t="s">
         <v>2175</v>
       </c>
       <c r="D12" s="35"/>
     </row>
-    <row r="13" spans="1:22" ht="203" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A13" s="34"/>
       <c r="C13" s="281" t="s">
         <v>2176</v>
       </c>
       <c r="D13" s="35"/>
     </row>
-    <row r="14" spans="1:22" ht="334" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:22" ht="331.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="36"/>
       <c r="B14" s="22"/>
       <c r="C14" s="282" t="s">
@@ -44252,15 +44263,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184EEBBB-E0CA-4F9C-AD01-12A158F96233}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.453125" customWidth="1"/>
-    <col min="2" max="2" width="60.36328125" customWidth="1"/>
-    <col min="3" max="3" width="58.90625" customWidth="1"/>
+    <col min="1" max="1" width="42.44140625" customWidth="1"/>
+    <col min="2" max="2" width="60.33203125" customWidth="1"/>
+    <col min="3" max="3" width="58.88671875" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>6</v>
       </c>
@@ -44270,7 +44281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>8</v>
       </c>
@@ -44282,7 +44293,7 @@
       </c>
       <c r="D2" s="20"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
@@ -44292,7 +44303,7 @@
       </c>
       <c r="D3" s="20"/>
     </row>
-    <row r="4" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>13</v>
       </c>
@@ -44304,7 +44315,7 @@
       </c>
       <c r="D4" s="20"/>
     </row>
-    <row r="5" spans="1:4" ht="116.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>15</v>
       </c>
@@ -44332,44 +44343,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X73"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="48.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="69.7265625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="73.81640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="56.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.1796875" style="11" customWidth="1"/>
-    <col min="8" max="8" width="43.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.90625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="67.90625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="66.36328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.81640625" style="11" customWidth="1"/>
-    <col min="13" max="13" width="39.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="48.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="92.453125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="60.54296875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="7.81640625" style="11" customWidth="1"/>
-    <col min="18" max="18" width="56.81640625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="54.36328125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="62.90625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="58.81640625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.81640625" style="12"/>
-    <col min="23" max="23" width="67.81640625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="68.36328125" style="1" customWidth="1"/>
-    <col min="25" max="26" width="59.36328125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="59.6328125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="99.453125" style="1" customWidth="1"/>
-    <col min="29" max="29" width="41.1796875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="125.08984375" style="1" customWidth="1"/>
-    <col min="31" max="16384" width="8.81640625" style="1"/>
+    <col min="1" max="2" width="48.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="69.77734375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="73.77734375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="56.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.21875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.88671875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="67.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="66.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.77734375" style="11" customWidth="1"/>
+    <col min="13" max="13" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="48.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="92.44140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="60.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="7.77734375" style="11" customWidth="1"/>
+    <col min="18" max="18" width="56.77734375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="54.33203125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="62.88671875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="58.77734375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.77734375" style="12"/>
+    <col min="23" max="23" width="67.77734375" style="2" customWidth="1"/>
+    <col min="24" max="24" width="68.33203125" style="1" customWidth="1"/>
+    <col min="25" max="26" width="59.33203125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="59.6640625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="99.44140625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="41.21875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="125.109375" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="8"/>
@@ -44390,7 +44401,7 @@
       <c r="U2" s="8"/>
       <c r="W2" s="8"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -44398,13 +44409,13 @@
       <c r="W3" s="1"/>
       <c r="X3" s="2"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>2277</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:24" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2278</v>
       </c>
@@ -44413,27 +44424,27 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>2224</v>
       </c>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:24" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="305" t="s">
         <v>2321</v>
       </c>
@@ -44445,7 +44456,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:24" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A12" s="305" t="s">
         <v>2322</v>
       </c>
@@ -44462,7 +44473,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A13" s="305" t="s">
         <v>2323</v>
       </c>
@@ -44476,7 +44487,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="116" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A14" s="305" t="s">
         <v>2324</v>
       </c>
@@ -44490,7 +44501,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A15" s="305" t="s">
         <v>2325</v>
       </c>
@@ -44507,12 +44518,12 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>2225</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>2319</v>
       </c>
@@ -44527,7 +44538,7 @@
       </c>
       <c r="E17" s="303"/>
     </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>2320</v>
       </c>
@@ -44542,14 +44553,14 @@
       </c>
       <c r="E18" s="303"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>2227</v>
       </c>
       <c r="D19" s="303"/>
       <c r="E19" s="303"/>
     </row>
-    <row r="20" spans="1:5" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>2318</v>
       </c>
@@ -44566,7 +44577,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>2317</v>
       </c>
@@ -44580,7 +44591,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>2316</v>
       </c>
@@ -44592,7 +44603,7 @@
       </c>
       <c r="D22" s="303"/>
     </row>
-    <row r="23" spans="1:5" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>2315</v>
       </c>
@@ -44609,7 +44620,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="174" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>2314</v>
       </c>
@@ -44626,12 +44637,12 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>2228</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>2309</v>
       </c>
@@ -44643,7 +44654,7 @@
       </c>
       <c r="D26" s="303"/>
     </row>
-    <row r="27" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>2310</v>
       </c>
@@ -44657,7 +44668,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>2311</v>
       </c>
@@ -44669,7 +44680,7 @@
       </c>
       <c r="D28" s="305"/>
     </row>
-    <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>2312</v>
       </c>
@@ -44681,7 +44692,7 @@
       </c>
       <c r="D29" s="305"/>
     </row>
-    <row r="30" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>2313</v>
       </c>
@@ -44693,12 +44704,12 @@
       </c>
       <c r="D30" s="305"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>2229</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>2326</v>
       </c>
@@ -44709,7 +44720,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>2331</v>
       </c>
@@ -44720,7 +44731,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>2334</v>
       </c>
@@ -44735,7 +44746,7 @@
       </c>
       <c r="E34" s="305"/>
     </row>
-    <row r="35" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>2332</v>
       </c>
@@ -44749,7 +44760,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>2335</v>
       </c>
@@ -44766,12 +44777,12 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>2230</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="306" t="s">
         <v>2345</v>
       </c>
@@ -44783,7 +44794,7 @@
       </c>
       <c r="D38" s="305"/>
     </row>
-    <row r="39" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="306" t="s">
         <v>2346</v>
       </c>
@@ -44795,7 +44806,7 @@
       </c>
       <c r="D39" s="305"/>
     </row>
-    <row r="40" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="306" t="s">
         <v>2351</v>
       </c>
@@ -44809,7 +44820,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="116" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A41" s="306" t="s">
         <v>2352</v>
       </c>
@@ -44823,7 +44834,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="306" t="s">
         <v>2356</v>
       </c>
@@ -44837,7 +44848,7 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="306" t="s">
         <v>2362</v>
       </c>
@@ -44851,12 +44862,12 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>2231</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>2382</v>
       </c>
@@ -44870,7 +44881,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>2383</v>
       </c>
@@ -44884,7 +44895,7 @@
         <v>2368</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>2384</v>
       </c>
@@ -44898,12 +44909,12 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>2232</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>2381</v>
       </c>
@@ -44917,7 +44928,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>2380</v>
       </c>
@@ -44931,7 +44942,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>2387</v>
       </c>
@@ -44945,7 +44956,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>2394</v>
       </c>
@@ -44959,7 +44970,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>2393</v>
       </c>
@@ -44976,7 +44987,7 @@
         <v>2395</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>2396</v>
       </c>
@@ -44990,7 +45001,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>2402</v>
       </c>
@@ -45007,7 +45018,7 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>2233</v>
       </c>
@@ -45015,7 +45026,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>2235</v>
       </c>
@@ -45023,7 +45034,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>2237</v>
       </c>
@@ -45031,47 +45042,47 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>2239</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>2240</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>2241</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>2242</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>2243</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>2244</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>2246</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>2247</v>
       </c>
@@ -45079,7 +45090,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>2249</v>
       </c>
@@ -45087,7 +45098,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>2251</v>
       </c>
@@ -45095,7 +45106,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>2253</v>
       </c>
@@ -45103,7 +45114,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>2255</v>
       </c>
@@ -45111,7 +45122,7 @@
         <v>2256</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>2257</v>
       </c>
@@ -45119,7 +45130,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>2259</v>
       </c>
